--- a/uploads/quiz-questions.xlsx
+++ b/uploads/quiz-questions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,259 +421,259 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>বাংলাদেশে কত ধরনের মৌসুমি বায়ু প্রবাহিত হয়?</v>
+        <v>নিচের কোনটি ভূমি সংরক্ষণের উপায়? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
       </c>
       <c r="B2" t="str">
-        <v>দুই</v>
+        <v>বৃক্ষনিধন</v>
       </c>
       <c r="C2" t="str">
-        <v>তিন</v>
+        <v>জৈব সার প্রয়োগ</v>
       </c>
       <c r="D2" t="str">
-        <v>চার</v>
+        <v>অধিক সেচ</v>
       </c>
       <c r="E2" t="str">
-        <v>পাঁচ</v>
+        <v>নিবিড় চাষ</v>
       </c>
       <c r="F2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>বায়ুমন্ডলের শতকরা কত ভাগ অক্সিজেন বিদ্যমান?</v>
+        <v>SRI পদ্ধতিতে ব্যবহৃত ধানের চারার বয়স কত?</v>
       </c>
       <c r="B3" t="str">
-        <v>৮০,০০ ভাগ</v>
+        <v>১০-১৫ দিন</v>
       </c>
       <c r="C3" t="str">
-        <v>৪০.৪০ ভাগ</v>
+        <v>২০-২৫ দিন</v>
       </c>
       <c r="D3" t="str">
-        <v>৫০.০৩ ভাগ</v>
+        <v>২৫-৩০ দিন</v>
       </c>
       <c r="E3" t="str">
-        <v>২০.৯৯ ভাগ</v>
+        <v>৩০-৩৫ দিন</v>
       </c>
       <c r="F3" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>জলবায়ু বলতে কত বছরের গড় অবস্থাকে বুঝায়?</v>
+        <v>এসআরআই পদ্ধতিতে প্রতি গুছিতে কয়টি চারা রোপণ করা যায়?</v>
       </c>
       <c r="B4" t="str">
-        <v>৫-১০</v>
+        <v>১টি</v>
       </c>
       <c r="C4" t="str">
-        <v>১০-১৫</v>
+        <v>২টি</v>
       </c>
       <c r="D4" t="str">
-        <v>২০-৩০</v>
+        <v>৩টি</v>
       </c>
       <c r="E4" t="str">
-        <v>৪০-৫০</v>
+        <v>৪ টি</v>
       </c>
       <c r="F4" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>বৃষ্টিকণা ঘণ্টায় কত মাইল বেগে মাটিতে পড়ে?</v>
+        <v>অম্লীয় মাটিতে কোন আয়নের পরিমাণ বেশি?</v>
       </c>
       <c r="B5" t="str">
-        <v>১৫ মাইল</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="C5" t="str">
-        <v>২০ মাইল</v>
+        <v>হাইড্রোক্সিল</v>
       </c>
       <c r="D5" t="str">
-        <v>২২ মাইল</v>
+        <v>সোডিয়াম</v>
       </c>
       <c r="E5" t="str">
-        <v>২৪ মাইল</v>
+        <v>ক্যালসিয়াম</v>
       </c>
       <c r="F5" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>নিচের কোনটির পার্থক্যের কারণে আবহাওয়া জলবায়ুর প্রধান তারতম্য হয়ে থাকে?</v>
+        <v>নিচের কোনটি প্রাকৃতিক উপায়ে ঘাটি সংশোধন পদ্ধতি?</v>
       </c>
       <c r="B6" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>চুন ব্যবহার</v>
       </c>
       <c r="C6" t="str">
-        <v>তুষারপাত</v>
+        <v>জৈবসার ব্যবহার</v>
       </c>
       <c r="D6" t="str">
-        <v>বায়ুপ্রবাহ</v>
+        <v>প্রচুর বৃষ্টিপাত</v>
       </c>
       <c r="E6" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>কাঠের ছাই ব্যবহার</v>
       </c>
       <c r="F6" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>কোন অঞ্চলে তাপমাত্রা সবচেয়ে বেশি থাকে? [পটিয়া সরকারি কলেজ, চট্টগ্রাম।]</v>
+        <v>অম্লমান অনুসারে মাটিকে কয় ভাগে ভাগ করা হয়েছে?</v>
       </c>
       <c r="B7" t="str">
-        <v>উত্তর মেরু</v>
+        <v>২</v>
       </c>
       <c r="C7" t="str">
-        <v>দক্ষিণ মেরু</v>
+        <v>৩</v>
       </c>
       <c r="D7" t="str">
-        <v>নিরক্ষীয় অঞ্চল</v>
+        <v>৪</v>
       </c>
       <c r="E7" t="str">
-        <v>বিষুবীর অঞ্চল</v>
+        <v>৫</v>
       </c>
       <c r="F7" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>কৃষির উপর কোনটি বেশি প্রভাব ফেলে? [নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>মাটির একক কণার পরস্পরিক অনুপাত দ্বারা সৃষ্ট স্থূলতা বা সূক্ষতাকে কী বলে?</v>
       </c>
       <c r="B8" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>রিবন</v>
       </c>
       <c r="C8" t="str">
-        <v>তাপমাত্রা</v>
+        <v>গঠন</v>
       </c>
       <c r="D8" t="str">
-        <v>আর্দ্রতা</v>
+        <v>সংযুক্তি</v>
       </c>
       <c r="E8" t="str">
-        <v>আলো</v>
+        <v>বুনট</v>
       </c>
       <c r="F8" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>সমুদ্রের নিকটবর্তী স্থানসমূহের আবহাওয়া কেমন হয়?</v>
+        <v>খাদ্য উৎপাদন বৃদ্ধি করতে প্রতিবছর কত হারে রাসায়নিক সারের ব্যবহার বৃদ্ধি পাচ্ছে?</v>
       </c>
       <c r="B9" t="str">
-        <v>চরমভাবাপন্ন</v>
+        <v>৫%</v>
       </c>
       <c r="C9" t="str">
-        <v>বিষমভাবাপন্ন</v>
+        <v>১০%</v>
       </c>
       <c r="D9" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>২০%</v>
       </c>
       <c r="E9" t="str">
-        <v>কোনটাই নয়</v>
+        <v>২৫%</v>
       </c>
       <c r="F9" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>কোন স্থানের দৈনন্দিন বায়ুমন্ডলের অবস্থাকে – বলে?</v>
+        <v>কোন মাটিতে ভূমিক্ষয় অপেক্ষাকৃত কম?</v>
       </c>
       <c r="B10" t="str">
-        <v>জলবায়ু</v>
+        <v>এঁটেল</v>
       </c>
       <c r="C10" t="str">
-        <v>আবহাওয়া</v>
+        <v>পলি এঁটেল</v>
       </c>
       <c r="D10" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>এঁটেল দোআঁশ</v>
       </c>
       <c r="E10" t="str">
-        <v>ঝড়</v>
+        <v>বেলে মাটি</v>
       </c>
       <c r="F10" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>কুয়াশার সময় আর্দ্রতা কত হয়?</v>
+        <v>ভূমির উপরিতল ঢেকে রেখে মাটি ও রস অপসারণ হয়ে যাওয়া প্রতিরোধ করাকে কী বলে?</v>
       </c>
       <c r="B11" t="str">
-        <v>৫০%</v>
+        <v>স্ট্রিপ ক্রপিং</v>
       </c>
       <c r="C11" t="str">
-        <v>৭০%</v>
+        <v>মালচিং</v>
       </c>
       <c r="D11" t="str">
-        <v>৯০%</v>
+        <v>মিক্স ক্রপিং</v>
       </c>
       <c r="E11" t="str">
-        <v>১০০%</v>
+        <v>রগিং</v>
       </c>
       <c r="F11" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>বাংলাদেশে গ্রীষ্মকালে সর্বনিম্ন তাপমাত্রা কত?</v>
+        <v>ক্ষারীয় ষাটিকে কোন নামে ডাকা হয়?</v>
       </c>
       <c r="B12" t="str">
-        <v>২০° - ২৮° সে.</v>
+        <v>সেলাইন মাটি</v>
       </c>
       <c r="C12" t="str">
-        <v>১৮° - ২৬° সে.</v>
+        <v>চুনযুক্ত মাটি</v>
       </c>
       <c r="D12" t="str">
-        <v>২২°-৩০° সে.</v>
+        <v>কৃষ্ণ ক্ষার</v>
       </c>
       <c r="E12" t="str">
-        <v>১৫° - ২২° সে.</v>
+        <v>ক্ষার মাটি</v>
       </c>
       <c r="F12" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>দিবা-দৈর্ঘ্যের ভিত্তিতে ফসলকে ভাগ করা যায়-</v>
+        <v>কোন ফসলটি মাটি ঢেকে রাখে ফলে ভূমিক্ষয় কম হয়?</v>
       </c>
       <c r="B13" t="str">
-        <v>তিন ভাগে</v>
+        <v>আখ</v>
       </c>
       <c r="C13" t="str">
-        <v>চার ভাগে</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="D13" t="str">
-        <v>দু ভাগে</v>
+        <v>চীনাবাদাম</v>
       </c>
       <c r="E13" t="str">
-        <v>কোনো ভাগ নেই</v>
+        <v>গম</v>
       </c>
       <c r="F13" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>নিরক্ষীয় অঞ্চলে কোনটি ভালো হয়?</v>
+        <v>ভূমিক্ষয়ের কারণ কোনটি?</v>
       </c>
       <c r="B14" t="str">
-        <v>পাট</v>
+        <v>ভূমির ঢাল</v>
       </c>
       <c r="C14" t="str">
-        <v>খেজুর</v>
+        <v>শস্য পর্যায়</v>
       </c>
       <c r="D14" t="str">
-        <v>গম</v>
+        <v>জৈব পদার্থ</v>
       </c>
       <c r="E14" t="str">
-        <v>বার্লি</v>
+        <v>চাষাবাদ</v>
       </c>
       <c r="F14" t="str">
         <v>A</v>
@@ -681,39 +681,39 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>গ্রীষ্মকালে এদেশে প্রচুর ফসল ফলে কেন? [কুমিল্লা সিটি কলেজ, কুমিল্লা]</v>
+        <v>AWD পদ্ধতির মূল লক্ষ্য কী?</v>
       </c>
       <c r="B15" t="str">
-        <v>অধিক তাপমাত্রা</v>
+        <v>পানি ও জ্বালানি সাশ্রয় করা</v>
       </c>
       <c r="C15" t="str">
-        <v>বাতাসের আর্দ্রতা বেশি</v>
+        <v>পোকামাকড়ের উপদ্রব কমানো</v>
       </c>
       <c r="D15" t="str">
-        <v>মৌসুমি জলবায়ু</v>
+        <v>ফলন বেশি হয়</v>
       </c>
       <c r="E15" t="str">
-        <v>পরিবেশের শুষ্কতা</v>
+        <v>ফসল আগাম পাকে</v>
       </c>
       <c r="F15" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>কোন স্থানের জলবায়ুকে বর্ণনা করতে কত বছরের আবহাওয়ার গড় নেওয়া হয়?</v>
+        <v>এসআরআই পদ্ধতিতে কোন ফসলে সেচ দেওয়া হয়?</v>
       </c>
       <c r="B16" t="str">
-        <v>১০ বছর</v>
+        <v>গম</v>
       </c>
       <c r="C16" t="str">
-        <v>২৫ বছর</v>
+        <v>ধান</v>
       </c>
       <c r="D16" t="str">
-        <v>৩০ বছর</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="E16" t="str">
-        <v>৪০ বছর</v>
+        <v>কাউন</v>
       </c>
       <c r="F16" t="str">
         <v>B</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>খরিপ-২ মৌসুমের সময়কাল কোনটি?</v>
+        <v>নদীর প্রবাহ বাধাপ্রাপ্ত হয়ে কিয়দংশ আবদ্ধ জলাশয়ে পরিণত হলে তাকে কি বলা হয়?</v>
       </c>
       <c r="B17" t="str">
-        <v>জানুয়ারি-মার্চ</v>
+        <v>হাওড়</v>
       </c>
       <c r="C17" t="str">
-        <v>এপ্রিল-জুন</v>
+        <v>বাঁওড়</v>
       </c>
       <c r="D17" t="str">
-        <v>জুলাই-অক্টোবর</v>
+        <v>প্লাবনভূমি</v>
       </c>
       <c r="E17" t="str">
-        <v>মার্চ-জুন</v>
+        <v>হ্রদ</v>
       </c>
       <c r="F17" t="str">
         <v>C</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>দীর্ঘ দিবা দৈর্ঘ্যে ফুল দেয় নিচের কোন উদ্ভিদ?</v>
+        <v>SRI পদ্ধতিতে কোন সেচ পদ্ধতি ব্যবহার করা হয়।</v>
       </c>
       <c r="B18" t="str">
-        <v>শিম</v>
+        <v>প্লাবন</v>
       </c>
       <c r="C18" t="str">
-        <v>পিঁয়াজ</v>
+        <v>এ ডব্লিউ ডি</v>
       </c>
       <c r="D18" t="str">
-        <v>টমেটো</v>
+        <v>ফোয়ারা</v>
       </c>
       <c r="E18" t="str">
-        <v>ফুলকপি</v>
+        <v>নালা</v>
       </c>
       <c r="F18" t="str">
         <v>B</v>
@@ -761,179 +761,179 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>বায়ুর আপেক্ষিক আর্দ্রতা কম হলে কোনটি ঘটে? [ উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+        <v>নিচের চিত্রটি লক্ষ কর এবং প্রশ্নের উত্তর দাও : Q. নির্দেশিত A চিত্রটি কোন ধরনের মাটিকে নির্দেশ করে?</v>
       </c>
       <c r="B19" t="str">
-        <v>বাষ্পীভবন ধীরে হয়</v>
+        <v>বেলে মাটি</v>
       </c>
       <c r="C19" t="str">
-        <v>বাষ্পীভবন দ্রুত হয়</v>
+        <v>পলি মাটি</v>
       </c>
       <c r="D19" t="str">
-        <v>বাষ্পীয়ভবন একই থাকে</v>
+        <v>দো-আঁশ মাটি</v>
       </c>
       <c r="E19" t="str">
-        <v>বাষ্পীভবন চলমান থাকে</v>
+        <v>এঁটেল মাটি</v>
       </c>
       <c r="F19" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>খরিপ-১ মৌসুমের সময়কাল কোনটি?</v>
+        <v>প্রাকৃতিক ভূমিক্ষয়ের কারণ কোনটি? [ঢাকা রেসিডেনসিয়াল মডেল কলেজ, ঢাকা; খুলনা পাবলিক কলেজ, খুলনা]</v>
       </c>
       <c r="B20" t="str">
-        <v>ডিসেম্বর-মার্চ</v>
+        <v>ভূমিকর্ষণ</v>
       </c>
       <c r="C20" t="str">
-        <v>মার্চ-জুন</v>
+        <v>জুমচাষ</v>
       </c>
       <c r="D20" t="str">
-        <v>মে - জুলাই</v>
+        <v>পাহাড় কাটা</v>
       </c>
       <c r="E20" t="str">
-        <v>আগস্ট - নভেম্বর</v>
+        <v>পানি প্রবাহ</v>
       </c>
       <c r="F20" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>নিচের কোনটি আলোক নিরপেক্ষ উদ্ভিদ?</v>
+        <v>এসআরআই পদ্ধতিতে রোপণকৃত চারার উপযুক্ত বয়স- [ডাঃ আব্দুর রাজ্জাক মিউনিসিপ্যাল কলেজ, যশোর]</v>
       </c>
       <c r="B21" t="str">
-        <v>ধান</v>
+        <v>১২ দিন</v>
       </c>
       <c r="C21" t="str">
-        <v>পাট</v>
+        <v>২০ দিন</v>
       </c>
       <c r="D21" t="str">
-        <v>আলু</v>
+        <v>৩৫ দিন</v>
       </c>
       <c r="E21" t="str">
-        <v>ভুট্টা</v>
+        <v>৩০ দিন</v>
       </c>
       <c r="F21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>দেশের সর্বোচ্চ তাপমাত্রা থাকে কোন মাসে?</v>
+        <v>ভূমির ক্ষয়রোধ কতভাবে করা যায়?</v>
       </c>
       <c r="B22" t="str">
-        <v>এপ্রিল - আগস্ট</v>
+        <v>২ ভাবে</v>
       </c>
       <c r="C22" t="str">
-        <v>মে - আগস্ট</v>
+        <v>৩ ভাবে</v>
       </c>
       <c r="D22" t="str">
-        <v>মার্চ - জুলাই</v>
+        <v>৪ ভাবে</v>
       </c>
       <c r="E22" t="str">
-        <v>মার্চ - সেপ্টেম্বর</v>
+        <v>৫ ভাবে</v>
       </c>
       <c r="F22" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>বায়ুর তাপমাত্রা হ্রাস বৃদ্ধির প্রধান কারণ- [ রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+        <v>জমিতে জৈব পদার্থের পরিমাণ শতকরা কত ভাগ থাকা উচিত?</v>
       </c>
       <c r="B23" t="str">
-        <v>অক্ষাংশ</v>
+        <v>১ ভাগ</v>
       </c>
       <c r="C23" t="str">
-        <v>আর্দ্রতা</v>
+        <v>৫ ভাগ</v>
       </c>
       <c r="D23" t="str">
-        <v>জলবায়ু</v>
+        <v>১০ ভাগ</v>
       </c>
       <c r="E23" t="str">
-        <v>দিনের দৈর্ঘ্য</v>
+        <v>২৫ ভাগ</v>
       </c>
       <c r="F23" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>নিচের কোনটি দীর্ঘ দিবা দৈর্ঘ্যের উদ্ভিদ?</v>
+        <v>অম্লীয় মাটি সংশোধনের প্রধান উপায় কী?</v>
       </c>
       <c r="B24" t="str">
-        <v>টমেটো</v>
+        <v>সালফার সার ব্যবহার করে</v>
       </c>
       <c r="C24" t="str">
-        <v>ফুলকপি</v>
+        <v>সবুজ সার ব্যবহার করে</v>
       </c>
       <c r="D24" t="str">
-        <v>শিম</v>
+        <v>চুন ব্যবহার করে</v>
       </c>
       <c r="E24" t="str">
-        <v>বাঁধাকপি</v>
+        <v>সেচের পানির মান উন্নয়ন করে</v>
       </c>
       <c r="F24" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ফসলের ফলন ও উৎপাদন নিয়ন্ত্রণ করে নিচের কোনটি?</v>
+        <v>ভূমিক্ষয় রোধ করা যায় কীভাবে?</v>
       </c>
       <c r="B25" t="str">
-        <v>আবহাওয়া</v>
+        <v>আগাছা দমনের মাধ্যমে</v>
       </c>
       <c r="C25" t="str">
-        <v>জলবায়ু</v>
+        <v>রাসায়নিক সার ব্যবহার করে</v>
       </c>
       <c r="D25" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>ফসল ব্যবস্থাপনা অবলম্বন করে</v>
       </c>
       <c r="E25" t="str">
-        <v>তাপমাত্রা</v>
+        <v>পাহাড়ের ঢাল কেটে</v>
       </c>
       <c r="F25" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>মৌসুমি জলবায়ুর দেশ কোনটি?</v>
+        <v>কর্দম মাটির কণার ব্যাস কত?</v>
       </c>
       <c r="B26" t="str">
-        <v>ভারত</v>
+        <v>.৫-১.০</v>
       </c>
       <c r="C26" t="str">
-        <v>বাংলাদেশ</v>
+        <v>.২৫-৫.০</v>
       </c>
       <c r="D26" t="str">
-        <v>ইংল্যান্ড</v>
+        <v>১.-২</v>
       </c>
       <c r="E26" t="str">
-        <v>পাকিস্তান</v>
+        <v>&lt;.০০২</v>
       </c>
       <c r="F26" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>কোনটি আলোক সংবেদনশীল ধানের জাত? [ঢাকা রেসিডেন্সিয়াল মডেল কলেজ, ঢাকা]</v>
+        <v>সেচের পানি মাটির অভ্যন্তরে কোথায় অবস্থান করে?</v>
       </c>
       <c r="B27" t="str">
-        <v>বি আর-১</v>
+        <v>মৃত্তিকা কণাতে</v>
       </c>
       <c r="C27" t="str">
-        <v>বি আর-৫</v>
+        <v>মৃত্তিকা ছিদ্রে</v>
       </c>
       <c r="D27" t="str">
-        <v>বি আর-২১</v>
+        <v>জৈব পদার্থে</v>
       </c>
       <c r="E27" t="str">
-        <v>বি আর-৩২</v>
+        <v>খনিজ পদার্থে</v>
       </c>
       <c r="F27" t="str">
         <v>B</v>
@@ -941,59 +941,59 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>টমেটোর ফুল ও ফল ধারণে কী রকম দিবা দৈর্ঘ্য প্রয়োজন? [পটিয়া সরকারি কলেজ, চট্টগ্রাম]</v>
+        <v>কাঠের ছাই কোন উপাদান সমৃদ্ধ?</v>
       </c>
       <c r="B28" t="str">
-        <v>স্বল্প দৈর্ঘ্য</v>
+        <v>ক্ষার</v>
       </c>
       <c r="C28" t="str">
-        <v>দীর্ঘ দৈর্ঘ্য</v>
+        <v>অম্ল</v>
       </c>
       <c r="D28" t="str">
-        <v>যেকোনোটা</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="E28" t="str">
-        <v>নিরপেক্ষ</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="F28" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>বাংলাদেশে সর্বোচ্চ বৃষ্টিপাত হয় কোথায়? [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
+        <v>মাটির উর্বরতা বৃদ্ধিতে কোনটি বেশি কার্যকরী?</v>
       </c>
       <c r="B29" t="str">
-        <v>লালপুরে</v>
+        <v>জৈব সার প্রয়োগ</v>
       </c>
       <c r="C29" t="str">
-        <v>লালখানে</v>
+        <v>রাসায়নিক সার প্রয়োগ</v>
       </c>
       <c r="D29" t="str">
-        <v>টেকনাফে</v>
+        <v>শস্য পর্যায় অবলম্বন</v>
       </c>
       <c r="E29" t="str">
-        <v>তেঁতুলিয়ায়</v>
+        <v>ভূমি ক্ষয় রোধ</v>
       </c>
       <c r="F29" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>বাংলাদেশে বাৎসরিক গড় বৃষ্টিপাতের পরিমাণ কত? [ জালালাবাদ কলেজ, সিলেট। ]</v>
+        <v>এসআরআই পদ্ধতিতে চারা রোপণের ক্ষেত্রে কোন পদ্ধতি অনুসরণ করা হয়?</v>
       </c>
       <c r="B30" t="str">
-        <v>২২২ সে.মি</v>
+        <v>আয়তাকার</v>
       </c>
       <c r="C30" t="str">
-        <v>২২৫ সে.মি.</v>
+        <v>ত্রিকোণাকার</v>
       </c>
       <c r="D30" t="str">
-        <v>২২৭ সে.মি.</v>
+        <v>ষড়ভুজাকার</v>
       </c>
       <c r="E30" t="str">
-        <v>২৩০ সে.মি.</v>
+        <v>বর্গাকার</v>
       </c>
       <c r="F30" t="str">
         <v>D</v>
@@ -1001,219 +1001,219 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ধান চাষের জন্য সর্বোত্তম তাপমাত্রা কত? [ অমৃত লাল দে মহাবিদ্যালয়, বরিশাল ]</v>
+        <v>মাটির উর্বরতা বৃদ্ধিতে কোনটি বেশি কার্যকরী? [শহীদ স্মৃতি কলেজ, ঢাকা; সরকারি শহীদ বুলবুল কলেজ, পাবনা]</v>
       </c>
       <c r="B31" t="str">
-        <v>১০° সে.</v>
+        <v>জৈব সার প্রয়োগ</v>
       </c>
       <c r="C31" t="str">
-        <v>২৫° সে</v>
+        <v>রাসায়নিক সার প্রয়োগ</v>
       </c>
       <c r="D31" t="str">
-        <v>৩৩° সে.</v>
+        <v>শস্য পর্যায় অবলম্বন</v>
       </c>
       <c r="E31" t="str">
-        <v>৪০° সে</v>
+        <v>ভূমি ক্ষয় রোধ</v>
       </c>
       <c r="F31" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>নিচের কোন উদ্ভিদের ক্ষেত্রে অন্ধকার কাল বিশেষ গুরুত্বপূর্ণ? [কুমিল্লা সিটি কলেজ, কুমিল্লা।]</v>
+        <v>সালফিউরিক এসিডের সংকেত কী?</v>
       </c>
       <c r="B32" t="str">
-        <v>বীট</v>
+        <v>$\mathrm{CaCO}_3$</v>
       </c>
       <c r="C32" t="str">
-        <v>সয়াবিন</v>
+        <v>$\mathrm{H}_2 \mathrm{SO}_4$</v>
       </c>
       <c r="D32" t="str">
-        <v>পাট</v>
+        <v>$\mathrm{CaO}$</v>
       </c>
       <c r="E32" t="str">
-        <v>আম</v>
+        <v>$\mathrm{HS}_2 \mathrm{P}$</v>
       </c>
       <c r="F32" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>অধিকাংশ ফসল কত তাপমাত্রায় ভালো হয়?</v>
+        <v>এসআরআই পদ্ধতিতে রোপণকৃত চারার উপযুক্ত বয়স-</v>
       </c>
       <c r="B33" t="str">
-        <v>১০-২০° সে.</v>
+        <v>১২ দিন</v>
       </c>
       <c r="C33" t="str">
-        <v>২৫-২৮° সে.</v>
+        <v>২০ দিন</v>
       </c>
       <c r="D33" t="str">
-        <v>২৩°-২৯° সে</v>
+        <v>৩৫ দিন</v>
       </c>
       <c r="E33" t="str">
-        <v>২৭°-৩১° সে.</v>
+        <v>৩০ দিন</v>
       </c>
       <c r="F33" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ধান গাছের অভিযোজনের জন্য সর্বনিম্ন তাপমাত্রা কত?</v>
+        <v>কোন ধরনের ভূমিক্ষয়ে প্রায় প্রতিবছর ২ কোটি টন মাটি স্থানচ্যুত হয়ে সাগরে চলে যায়?</v>
       </c>
       <c r="B34" t="str">
-        <v>২° সে.</v>
+        <v>পানি ভূমিক্ষয়</v>
       </c>
       <c r="C34" t="str">
-        <v>৫° সে.</v>
+        <v>ধস ভূমিক্ষয়</v>
       </c>
       <c r="D34" t="str">
-        <v>৮০°সে.</v>
+        <v>পাত ভূমিক্ষয়</v>
       </c>
       <c r="E34" t="str">
-        <v>১০° সে.</v>
+        <v>গালি ভূমিক্ষয়</v>
       </c>
       <c r="F34" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>বাংলাদেশে গ্রীষ্মকালে কোন মৌসুমি বায়ুর প্রভাবে বৃষ্টিপাত হয়?</v>
+        <v>মাটির আর্দ্রতা সংরক্ষণের কৃত্রিম পদ্ধতিকে কী বলা হয়?</v>
       </c>
       <c r="B35" t="str">
-        <v>উত্তর - পশ্চিম</v>
+        <v>সেচ</v>
       </c>
       <c r="C35" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>নিকাশ</v>
       </c>
       <c r="D35" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>মৃত্তিকা সংরক্ষণ</v>
       </c>
       <c r="E35" t="str">
-        <v>উত্তর - পূর্ব</v>
+        <v>মালচিং</v>
       </c>
       <c r="F35" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ফসলের পরিচর্যায় প্রভাব বিস্তার করে নিচের কোনটি?</v>
+        <v>ভূমিক্ষয় রোধ করার উপায়? [হলি ল্যান্ড কলেজ, দিনাজপুর]</v>
       </c>
       <c r="B36" t="str">
-        <v>বায়ুর আর্দ্রতা</v>
+        <v>মালচিং</v>
       </c>
       <c r="C36" t="str">
-        <v>সূর্যালোক</v>
+        <v>পশুচারণ</v>
       </c>
       <c r="D36" t="str">
-        <v>আবহাওয়া</v>
+        <v>জুমচাষ</v>
       </c>
       <c r="E36" t="str">
-        <v>মাটি</v>
+        <v>পানি প্রবাহ</v>
       </c>
       <c r="F36" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>উত্তর-পশ্চিম মৌসুমি বায়ু প্রবাহিত হয় কোন দিক দিয়ে? [শহীদ বুলবুল সরকারি কলেজ, পাবনা।]</v>
+        <v>মাটির ক্ষারকত্ব নিয়ন্ত্রণে কোন পুষ্টি উৎপাদন যোগ করতে হয়।</v>
       </c>
       <c r="B37" t="str">
-        <v>স্থলভাগ থেকে জলভাগ</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="C37" t="str">
-        <v>জলভাগ থেকে স্থলভাগ</v>
+        <v>ফসফরাস</v>
       </c>
       <c r="D37" t="str">
-        <v>স্থলভাগ থেকে মরুভূমি</v>
+        <v>সালফার</v>
       </c>
       <c r="E37" t="str">
-        <v>সমভূমি থেকে জলভাগ</v>
+        <v>পটাশ</v>
       </c>
       <c r="F37" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>জলবায়ু আবহাওয়ার কত বছরের গড়?</v>
+        <v>সমন্বিত ধান চাষ পদ্ধতি (SRI) কত সালে আবিষ্কৃত হয়।</v>
       </c>
       <c r="B38" t="str">
-        <v>২৫-৩০ বছর</v>
+        <v>১৯৭৫ সালে</v>
       </c>
       <c r="C38" t="str">
-        <v>২০-২৫ বছর</v>
+        <v>১৯৮০ সালে</v>
       </c>
       <c r="D38" t="str">
-        <v>১৫-২০ বছর</v>
+        <v>১৯৮৫ সালে</v>
       </c>
       <c r="E38" t="str">
-        <v>১৫-২৫ বছর</v>
+        <v>১৯৯০ সালে</v>
       </c>
       <c r="F38" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ধান গাছের জন্য সর্বোত্তম তাপমাত্রা কত?</v>
+        <v>পাহাড়ি এলাকায় সাধারণত কোন পদ্ধতিতে চাষাবাদ করার ফলেভূমিক্ষয় হয়।</v>
       </c>
       <c r="B39" t="str">
-        <v>১০-২০°  সে.</v>
+        <v>সোপান চাষ</v>
       </c>
       <c r="C39" t="str">
-        <v>২০-৩০° সে.</v>
+        <v>কন্টোর চাষ</v>
       </c>
       <c r="D39" t="str">
-        <v>৩০-৪০° সে.</v>
+        <v>ধাপ চাষ</v>
       </c>
       <c r="E39" t="str">
-        <v>২৫-৩৫° সে</v>
+        <v>জূম  চাষ</v>
       </c>
       <c r="F39" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>বায়ুর আর্দ্রতা বেশি হলে ফসল উৎপাদনের ক্ষেত্রে কি ধরনের প্রভাব পড়তে পারে?</v>
+        <v>শুকানো সবজিতে জলীয় অংশ কত থাকে?</v>
       </c>
       <c r="B40" t="str">
-        <v>পানির ঘাটতি হয়</v>
+        <v>৬-৮%</v>
       </c>
       <c r="C40" t="str">
-        <v>প্রস্বেদন বেড়ে যায়</v>
+        <v>৬০-৮০%</v>
       </c>
       <c r="D40" t="str">
-        <v>ফলন কমিয়ে দেয়</v>
+        <v>১৬-১৮%</v>
       </c>
       <c r="E40" t="str">
-        <v>পোকা ও রোগের আক্রমণ বেড়ে যায়</v>
+        <v>২৬-২৮%</v>
       </c>
       <c r="F40" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>রবি ফসল নিচের কোনটি?</v>
+        <v>কোনটিকে সূক্ষ্ম বুনট মাটি বলা হয়?</v>
       </c>
       <c r="B41" t="str">
-        <v>পাট</v>
+        <v>পলি</v>
       </c>
       <c r="C41" t="str">
-        <v>ভুট্টা</v>
+        <v>বেলে</v>
       </c>
       <c r="D41" t="str">
-        <v>তামাক</v>
+        <v>এঁটেল</v>
       </c>
       <c r="E41" t="str">
-        <v>তিল</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="F41" t="str">
         <v>C</v>
@@ -1221,59 +1221,59 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>বৃষ্টিপাত মাপার যন্ত্রের নাম কোনটি? [ কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ ]</v>
+        <v>শিম জাতীয় শস্য চাষ করলে কোনটি সংযোজন হয়?</v>
       </c>
       <c r="B42" t="str">
-        <v>হাইগ্রোমিটার</v>
+        <v>অক্সিজেন</v>
       </c>
       <c r="C42" t="str">
-        <v>হাইড্রোমিটার</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="D42" t="str">
-        <v>থার্মোমিটার</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="E42" t="str">
-        <v>রেইনগেজ</v>
+        <v>কার্বন ডাইঅক্সাইড</v>
       </c>
       <c r="F42" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>আলোর পরিমাণ নিচের কোনটির ওপর নির্ভর করে? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ, কুমিল্লা।]</v>
+        <v>কোন মাটির পানি ধারণ ক্ষমতা সবচেয়ে কম?</v>
       </c>
       <c r="B43" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>এঁটেল</v>
       </c>
       <c r="C43" t="str">
-        <v>তাপমাত্রা</v>
+        <v>পলি</v>
       </c>
       <c r="D43" t="str">
-        <v>অক্ষাংশ</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="E43" t="str">
-        <v>দ্রাঘিমাংশ</v>
+        <v>বেলে</v>
       </c>
       <c r="F43" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>শীতকালে কোন দিক থেকে বায়ু আসে?</v>
+        <v>কোন উপাদানটিকে ‘মাটির প্রাণ' বলা হয়?</v>
       </c>
       <c r="B44" t="str">
-        <v>দক্ষিণ ও দক্ষিণ-পশ্চিম দিক</v>
+        <v>বায়ু</v>
       </c>
       <c r="C44" t="str">
-        <v>পূর্ব ও পূর্ব-উত্তর দিক</v>
+        <v>পানি</v>
       </c>
       <c r="D44" t="str">
-        <v>উত্তর ও উত্তর-পশ্চিম দিক</v>
+        <v>জৈব পদার্থ</v>
       </c>
       <c r="E44" t="str">
-        <v>দক্ষিণ ও দক্ষিণ-পূর্ব দিক</v>
+        <v>খনিজ পদার্থ</v>
       </c>
       <c r="F44" t="str">
         <v>C</v>
@@ -1281,79 +1281,79 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>বাংলাদেশে সাধারণত কোন মাসে শিলাবৃষ্টি হয়?</v>
+        <v>মাটির অম্লত্ব বাড়ে কোনটির জন্য?</v>
       </c>
       <c r="B45" t="str">
-        <v>জানুয়ারি-ফেব্রুয়ারি</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="C45" t="str">
-        <v>ফেব্রুয়ারি-মার্চ</v>
+        <v>হাইড্রোক্সিল</v>
       </c>
       <c r="D45" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="E45" t="str">
-        <v>এপ্রিল-মে</v>
+        <v>সালফার</v>
       </c>
       <c r="F45" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>সাধারণত আগাম আকস্মিক বন্যা কোন মাসে হয়?</v>
+        <v>কোন মাটিতে সূক্ষ্মকণা বেশি থাকে?</v>
       </c>
       <c r="B46" t="str">
-        <v>মার্চ - এপ্রিল</v>
+        <v>এঁটেল</v>
       </c>
       <c r="C46" t="str">
-        <v>এপ্রিল - মে</v>
+        <v>বেলে</v>
       </c>
       <c r="D46" t="str">
-        <v>মে - জুন</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="E46" t="str">
-        <v>জুন - জুলাই</v>
+        <v>এঁটেল-দোআঁশ</v>
       </c>
       <c r="F46" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>বড় দিনের উদ্ভিদের ফুল ফোটার জন্য কত ঘণ্টার বেশি আলো প্রয়োজন? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর।]</v>
+        <v>কুমড়া, লাউ ইত্যাদি বাগানে সেচ দেওয়া হয় কোন পদ্ধতিতে?</v>
       </c>
       <c r="B47" t="str">
-        <v>৫ ঘণ্টা</v>
+        <v>আইল পদ্ধতিতে</v>
       </c>
       <c r="C47" t="str">
-        <v>৮ ঘণ্টা</v>
+        <v>নালা পদ্ধতিতে</v>
       </c>
       <c r="D47" t="str">
-        <v>১০ ঘণ্টা</v>
+        <v>ড্রিপ পদ্ধতিতে</v>
       </c>
       <c r="E47" t="str">
-        <v>১২ ঘণ্টা</v>
+        <v>রিং বেসিন পদ্ধতিতে</v>
       </c>
       <c r="F47" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>নিচের কোনটি বাধাহীন দীর্ঘ দিবসী উদ্ভিদ? [রাজউক উত্তরা মডেল কলেজ, ঢাকা।]</v>
+        <v>বাংলাদেশের মাটিতে শতকরা কত ভাগ জৈব পদার্থ রয়েছে?</v>
       </c>
       <c r="B48" t="str">
-        <v>পিটুনিয়া</v>
+        <v>১ ভাগ</v>
       </c>
       <c r="C48" t="str">
-        <v>আনারস</v>
+        <v>২ ভাগ</v>
       </c>
       <c r="D48" t="str">
-        <v>আমন ধান</v>
+        <v>১.৫ ভাগ</v>
       </c>
       <c r="E48" t="str">
-        <v>গাঁদা ফুল</v>
+        <v>২.৫ ভাগ</v>
       </c>
       <c r="F48" t="str">
         <v>A</v>
@@ -1361,39 +1361,39 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>খরিপ-১ মৌসুমের ফসল কোনটি?</v>
+        <v>মাটির pH মান কত থাকলে গাছ সহজেই পুষ্টি উপাদান গ্রহণ করতে পারে</v>
       </c>
       <c r="B49" t="str">
-        <v>পাট</v>
+        <v>pH = ৪- ৫</v>
       </c>
       <c r="C49" t="str">
-        <v>মুগ</v>
+        <v>pH = ৫ - ৬</v>
       </c>
       <c r="D49" t="str">
-        <v>শিম</v>
+        <v>pH = ৬-৮</v>
       </c>
       <c r="E49" t="str">
-        <v>পেঁয়াজ</v>
+        <v>pH = ৮- ১০</v>
       </c>
       <c r="F49" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>যে সকল উদ্ভিদ দিন বা রাতের দৈর্ঘ্য দ্বারা প্রভাবিত হয় না তাদের কী বলে?</v>
+        <v>পাহাড়ি ভূমিক্ষয় রোধের প্রধান উপায়- [শহীদ পুলিশ স্মৃতি কলেজ, ঢাকা]</v>
       </c>
       <c r="B50" t="str">
-        <v>ছোট দিনের উদ্ভিদ</v>
+        <v>ঢালে ফসলের চাষ না করা</v>
       </c>
       <c r="C50" t="str">
-        <v>নিরপেক্ষ উদ্ভিদ</v>
+        <v>ধাপে চাষ</v>
       </c>
       <c r="D50" t="str">
-        <v>বড় দিনের উদ্ভিদ</v>
+        <v>জমির কম চাষ করা</v>
       </c>
       <c r="E50" t="str">
-        <v>স্বল্প দিবা দৈর্ঘ্য উদ্ভিদ</v>
+        <v>জাবড়া প্রয়োগ করা</v>
       </c>
       <c r="F50" t="str">
         <v>B</v>
@@ -1401,39 +1401,39 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>আলোক অসংবেদনশীল ফসলের জাত কোনটি? [বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>যদি কোনো মাটিতে প্রায় ৫০% বালি এবং ৫০% পলি ও কর্দম কণা থাকে, তবে তাকে কী মাটি বলে?</v>
       </c>
       <c r="B51" t="str">
-        <v>ব্রিধান-৪৩</v>
+        <v>দোআঁশ বেলে</v>
       </c>
       <c r="C51" t="str">
-        <v>ব্রিধান-৩০</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D51" t="str">
-        <v>ব্রিধান-৩১</v>
+        <v>বেলে এঁটেল</v>
       </c>
       <c r="E51" t="str">
-        <v>ব্রিধান-৫১</v>
+        <v>পলি এঁটেল</v>
       </c>
       <c r="F51" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>বড় দিনের উদ্ভিদের ক্ষেত্রে আলোককালের সময়সীমা কোনটি?</v>
+        <v>সেচের পানির কার্যকারিতা বৃদ্ধি করা যায়-</v>
       </c>
       <c r="B52" t="str">
-        <v>১০-১২ ঘণ্টা</v>
+        <v>দিনে দুইবার সেচ দিয়ে</v>
       </c>
       <c r="C52" t="str">
-        <v>১১-১৩ ঘণ্টা</v>
+        <v>আগাছা দমন করে</v>
       </c>
       <c r="D52" t="str">
-        <v>১৪-১৮ ঘণ্টা</v>
+        <v>সময়মতো সেচ দিয়ে</v>
       </c>
       <c r="E52" t="str">
-        <v>১৬-২০ ঘণ্টা</v>
+        <v>সকালবেলা সেচ দিয়ে</v>
       </c>
       <c r="F52" t="str">
         <v>C</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>খরার কারণে শতকরা কতভাগ ফলন হ্রাস পায়? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ। ]</v>
+        <v>কোন মাটির পানি ধারণ ক্ষমতা সবচেয়ে বেশি?</v>
       </c>
       <c r="B53" t="str">
-        <v>১৫-৩০</v>
+        <v>দোআঁশ বেলে</v>
       </c>
       <c r="C53" t="str">
-        <v>৩০ - ৭০</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D53" t="str">
-        <v>৫০ - ৭০</v>
+        <v>পলি</v>
       </c>
       <c r="E53" t="str">
-        <v>১৫ - ৯০</v>
+        <v>এঁটেল</v>
       </c>
       <c r="F53" t="str">
         <v>D</v>
@@ -1461,259 +1461,259 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>কোনো অঞ্চলের ফসলের প্রকার ও জাত নির্বাচনে কোনটি প্রভাব ফেলে? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+        <v>বায়ুর সাথে লাফিয়ে মৃত্তিকা কণার স্থানান্তর হওয়াকে কি বলে? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B54" t="str">
-        <v>জলবায়ু</v>
+        <v>সয়েল ক্রিপ</v>
       </c>
       <c r="C54" t="str">
-        <v>আবহাওয়া</v>
+        <v>স্প্ল্যাস ইরোসন</v>
       </c>
       <c r="D54" t="str">
-        <v>বায়ুর চাপ</v>
+        <v>সেল্টেশন</v>
       </c>
       <c r="E54" t="str">
-        <v>তাপমাত্রা</v>
+        <v>শীট ইরোসন</v>
       </c>
       <c r="F54" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>কোনো স্থানের দৈনন্দিন বায়ুমন্ডলের অবস্থাকে কী বলে? [ কালেক্টরেট স্কুল এন্ড কলেজ, রংপুর ]</v>
+        <v>নিচের তথ্যের ভিত্তিতে প্রশ্নের উত্তর দাও : জনৈক কৃষক তার জমির মাটি পরীক্ষা করে অম্লমান ৫.৫ পেলেন । Q. SRDI এর শ্রেণিবিভাগ অনুযায়ী কৃষকের জমির মাটি কোন শ্রেণির?</v>
       </c>
       <c r="B55" t="str">
-        <v>আবহাওয়া</v>
+        <v>অধিক অম্লীয়</v>
       </c>
       <c r="C55" t="str">
-        <v>জলবায়ু</v>
+        <v>সামান্য অম্লীয়</v>
       </c>
       <c r="D55" t="str">
-        <v>বায়ুপুঞ্জ</v>
+        <v>নিরপেক্ষ</v>
       </c>
       <c r="E55" t="str">
-        <v>বায়ুচাপ</v>
+        <v>সামান্য ক্ষারীয়</v>
       </c>
       <c r="F55" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ফসলের আলোক সংবেদনশীলতা সম্পর্কে সর্বপ্রথম ধারণা প্রদান করেন কে?</v>
+        <v>গমের ক্ষেতে প্রথম সেচটি কখন দেওয়া প্রয়োজন হয়?</v>
       </c>
       <c r="B56" t="str">
-        <v>গার্নার ও অ্যালার্ড</v>
+        <v>কুশি গজানোর সময়</v>
       </c>
       <c r="C56" t="str">
-        <v>গার্নার ও ম্যাকওয়ার্থ</v>
+        <v>শীষ গজানোর সময়</v>
       </c>
       <c r="D56" t="str">
-        <v>রিচার্ড ও গার্নার</v>
+        <v>মুকুট মূল গজানোর সময়</v>
       </c>
       <c r="E56" t="str">
-        <v>ডোনাল্ড ম্যাকওয়ার্থ</v>
+        <v>পুষ্পায়নের সময়</v>
       </c>
       <c r="F56" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>দিবা দৈর্ঘ্য নিরপেক্ষ উদ্ভিদ কোনটি?</v>
+        <v>হাইড্রোজেন আয়নের মান কমলে আমানের কী পরিবর্তন হবে?</v>
       </c>
       <c r="B57" t="str">
-        <v>পিঁয়াজ</v>
+        <v>বাড়বে</v>
       </c>
       <c r="C57" t="str">
-        <v>আলু</v>
+        <v>শূণ্য হবে</v>
       </c>
       <c r="D57" t="str">
-        <v>সূর্যমুখী</v>
+        <v>পরিবর্তন হবে না।</v>
       </c>
       <c r="E57" t="str">
-        <v>শিম</v>
+        <v>কমবে</v>
       </c>
       <c r="F57" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>বায়ুর আর্দ্রতা নির্ণায়ক যন্ত্রের নাম কী? [ঢাকা রেসিডেন্সিয়াল মডেল কলেজ, ঢাকা।]</v>
+        <v>অম্লমান অনুসারে মাটিকে কয় ভাগে ভাগ করা হয়?</v>
       </c>
       <c r="B58" t="str">
-        <v>ব্যারোমিটার</v>
+        <v>২</v>
       </c>
       <c r="C58" t="str">
-        <v>ল্যাকটোমিটার</v>
+        <v>৩</v>
       </c>
       <c r="D58" t="str">
-        <v>হাইগ্রোমিটার</v>
+        <v>৪</v>
       </c>
       <c r="E58" t="str">
-        <v>থার্মোমিটার</v>
+        <v>৫</v>
       </c>
       <c r="F58" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>মৌসুমি বায়ুর প্রভাবে কোনটি হয়? [ অমৃত লাল দে মহাবিদ্যালয়, বরিশাল। ]</v>
+        <v>মাটির অম্লত্ব সৃষ্টি হয় প্রধানত কোন উপাদানটির কারণে?</v>
       </c>
       <c r="B59" t="str">
-        <v>তুষারপাত</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="C59" t="str">
-        <v>শীত</v>
+        <v>হাইড্রোক্সিল</v>
       </c>
       <c r="D59" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="E59" t="str">
-        <v>জলপাত</v>
+        <v>গন্ধক</v>
       </c>
       <c r="F59" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>বাংলাদেশে বছরব্যাপী বৃষ্টিপাতের তারতম্যের কারণ কোনটি?</v>
+        <v>মাটির বিভিন্ন প্রকার পুষ্টি উপাদানের সহজলভ্যতা কিসের উপর নির্ভর করে? [মাইলস্টোন কলেজ, ঢাকা]</v>
       </c>
       <c r="B60" t="str">
-        <v>ভৌগোলিক অবস্থান</v>
+        <v>মাটির উর্বরতা</v>
       </c>
       <c r="C60" t="str">
-        <v>অক্ষাংশ</v>
+        <v>মাটির ক্ষারত্বের তীব্রতা</v>
       </c>
       <c r="D60" t="str">
-        <v>দ্রাঘিমাংশ</v>
+        <v>মাটির অম্লত্বের তীব্রতা</v>
       </c>
       <c r="E60" t="str">
-        <v>স্থলভাগের তারতাম্য</v>
+        <v>মাটির উৎপাদন ক্ষমতা</v>
       </c>
       <c r="F60" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>বায়ুমন্ডলে কয়টি স্তর রয়েছে? [সোনার বাংলা বিশ্ববিদ্যালয় কলেজ, কুমিল্লা ]</v>
+        <v>ক্ষারীয় মাটি সংশোধন করা হয়-</v>
       </c>
       <c r="B61" t="str">
-        <v>২</v>
+        <v>জমিতে চুন প্রয়োগ করে</v>
       </c>
       <c r="C61" t="str">
-        <v>৩</v>
+        <v>সালফার সার ব্যবহার করে</v>
       </c>
       <c r="D61" t="str">
-        <v>৪</v>
+        <v>এঁটেল মাটি প্রয়োগ করা</v>
       </c>
       <c r="E61" t="str">
-        <v>৫</v>
+        <v>বেলে মাটি প্রয়োগ করে</v>
       </c>
       <c r="F61" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>নিচের কোনটি জলবায়ুর বৈশিষ্ট্য?</v>
+        <v>সমন্বিত ধান চাষ পদ্ধতি (SRI) কত সালে আবিষ্কৃত হয়? [হাজী লালমিয়া সিটি বিশ্ববিদ্যালয় কলেজ, গোপালগঞ্জ]</v>
       </c>
       <c r="B62" t="str">
-        <v>অপরিবর্তনশীল</v>
+        <v>১৯৭৫ সালে</v>
       </c>
       <c r="C62" t="str">
-        <v>ধীরে পরিবর্তনশীল</v>
+        <v>১৯৮০ সালে</v>
       </c>
       <c r="D62" t="str">
-        <v>মাটির গুণাবলিতে প্রভাব ফেলে</v>
+        <v>১৯৮৫ সালে</v>
       </c>
       <c r="E62" t="str">
-        <v>মৌসুমি বায়ুপ্রবাহ দ্বারা প্রভাবিত</v>
+        <v>১৯৯০ সালে</v>
       </c>
       <c r="F62" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>পাট চাষের জন্য সর্বোত্তম তাপমাত্রা নিচের কোনটি? [ কুমিল্লা সিটি কলেজ, কুমিল্লা]</v>
+        <v>কোন মাটিতে ভূমিক্ষয় অপেক্ষাকৃত কম? [হলি ল্যান্ড কলেজ, দিনাজপুর]</v>
       </c>
       <c r="B63" t="str">
-        <v>৪০ ডিগ্রি ফা.</v>
+        <v>এঁটেল</v>
       </c>
       <c r="C63" t="str">
-        <v>৬৫ ডিগ্রি ফা.</v>
+        <v>পলি এঁটেল</v>
       </c>
       <c r="D63" t="str">
-        <v>৯০ ডিগ্রি ফা.</v>
+        <v>এঁটেল দোআঁশ</v>
       </c>
       <c r="E63" t="str">
-        <v>৫০ ডিগ্রি ফা.</v>
+        <v>বেলে মাটি</v>
       </c>
       <c r="F63" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>বাংলাদেশের জলবায়ুর ধরন কেমন? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ]</v>
+        <v>মাটি সংশোধনে নিচের কোনটি জৈব বালাইনাশক</v>
       </c>
       <c r="B64" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>ক্লোরোপিকরিন</v>
       </c>
       <c r="C64" t="str">
-        <v>চরমভাবাপন্ন</v>
+        <v>ফরমালিন</v>
       </c>
       <c r="D64" t="str">
-        <v>নিরক্ষীয়</v>
+        <v>মিথাইল ব্রোমাইড</v>
       </c>
       <c r="E64" t="str">
-        <v>উষ্ণমণ্ডলীয়</v>
+        <v>নিমবিসিডন</v>
       </c>
       <c r="F64" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>গ্রীষ্মকালে মৌসুমি বায়ু কোন দিক দিয়ে প্রবাহিত হয়? [আবদুল কাদির মোল্লা সিটি কলেজ, নরসিংদী। ]</v>
+        <v>কোন মাটিতে সবচেয়ে ভালো ফসল জন্মে?</v>
       </c>
       <c r="B65" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>বেলে মাটি</v>
       </c>
       <c r="C65" t="str">
-        <v>উত্তর-দক্ষিণ</v>
+        <v>বেলে</v>
       </c>
       <c r="D65" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>পলি মাটি</v>
       </c>
       <c r="E65" t="str">
-        <v>উত্তর-পূর্ব</v>
+        <v>দোআঁশ মাটি</v>
       </c>
       <c r="F65" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>বাংলাদেশে কয় ধরনের মৌসুমি বায়ু প্রবাহিত হয়? [ ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, রংপুর ]</v>
+        <v>পাহাড়ি ঢালে ভূমি সংরক্ষণের উপায় কোনটি?</v>
       </c>
       <c r="B66" t="str">
-        <v>২</v>
+        <v>স্ট্রিপ ক্রপিং</v>
       </c>
       <c r="C66" t="str">
-        <v>৩</v>
+        <v>মালচিং</v>
       </c>
       <c r="D66" t="str">
-        <v>৪</v>
+        <v>মিশ্র চাষ</v>
       </c>
       <c r="E66" t="str">
-        <v>৫</v>
+        <v>শস্যপর্যায়</v>
       </c>
       <c r="F66" t="str">
         <v>A</v>
@@ -1721,119 +1721,119 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>খাটো দিবা দৈর্ঘ্যের উদ্ভিদ কোনটি?</v>
+        <v>মাটি অম্ল হবার জন্য দায়ী কোনটি?</v>
       </c>
       <c r="B67" t="str">
-        <v>পিঁয়াজ</v>
+        <v>অধিক চুন ব্যবহার</v>
       </c>
       <c r="C67" t="str">
-        <v>টমেটো</v>
+        <v>ইউরিয়া ব্যবহার</v>
       </c>
       <c r="D67" t="str">
-        <v>ভুট্টা</v>
+        <v>জৈবসার ব্যবহার</v>
       </c>
       <c r="E67" t="str">
-        <v>শিশ</v>
+        <v>সোডিয়াম থাকার জন্য</v>
       </c>
       <c r="F67" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>বাংলাদেশে কতটি কৃষি আবহাওয়া কেন্দ্র আছে?</v>
+        <v>নিচের ছকটি লক্ষ্য কর এবং প্রশ্নের উত্তর দাও: Q. ছকে 'C' মৃত্তিকা কী নির্দেশ করে?</v>
       </c>
       <c r="B68" t="str">
-        <v>৮</v>
+        <v>অম্লীয়</v>
       </c>
       <c r="C68" t="str">
-        <v>১০</v>
+        <v>নিরপেক্ষ</v>
       </c>
       <c r="D68" t="str">
-        <v>১২</v>
+        <v>লবণাক্ত</v>
       </c>
       <c r="E68" t="str">
-        <v>১৪</v>
+        <v>ক্ষারীয়</v>
       </c>
       <c r="F68" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>গ্রীষ্মকালে সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>পিএইচ স্কেলে মানের সর্বোচ্চ সীমা কত?</v>
       </c>
       <c r="B69" t="str">
-        <v>৩০°-৪১° সে.</v>
+        <v>৫</v>
       </c>
       <c r="C69" t="str">
-        <v>৩৫°-৪৭° সে.</v>
+        <v>৭</v>
       </c>
       <c r="D69" t="str">
-        <v>২৮°-৪২° সে</v>
+        <v>১২</v>
       </c>
       <c r="E69" t="str">
-        <v>৩০°-৪৮° সে.</v>
+        <v>১৪</v>
       </c>
       <c r="F69" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>কোনটি বড় দিনের উদ্ভিদ?</v>
+        <v>ফসল চাষের জন্য সবচেয়ে উপযোগী-</v>
       </c>
       <c r="B70" t="str">
-        <v>গম</v>
+        <v>বেলে মাটি</v>
       </c>
       <c r="C70" t="str">
-        <v>সরিষা</v>
+        <v>দোঁ-আশ মাটি</v>
       </c>
       <c r="D70" t="str">
-        <v>চীনাবাদাম</v>
+        <v>পলি মাটি</v>
       </c>
       <c r="E70" t="str">
-        <v>চিচিঙ্গা</v>
+        <v>এঁটেল মাটি</v>
       </c>
       <c r="F70" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>বাতাসের আর্দ্রতা বেশি হলে প্রস্বেদন-</v>
+        <v>লিটমাস পেপার ছারা কী মাপা হয়?</v>
       </c>
       <c r="B71" t="str">
-        <v>বেড়ে যায়</v>
+        <v>অম্লমান</v>
       </c>
       <c r="C71" t="str">
-        <v>কমে যায়</v>
+        <v>আর্দ্রতা</v>
       </c>
       <c r="D71" t="str">
-        <v>একই থাকে</v>
+        <v>বৃষ্টিপাত</v>
       </c>
       <c r="E71" t="str">
-        <v>চলমান থাকে</v>
+        <v>তাপমাত্রা</v>
       </c>
       <c r="F71" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>আর্দ্র মৌসুমি বায়ু প্রবাহিত হয় কোন দিক দিয়ে?</v>
+        <v>নিচের কোনটি ভূমি সংরক্ষণের উপায়?</v>
       </c>
       <c r="B72" t="str">
-        <v>উত্তর-পূর্ব</v>
+        <v>বৃক্ষনিধন</v>
       </c>
       <c r="C72" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>জৈব সার প্রয়োগ</v>
       </c>
       <c r="D72" t="str">
-        <v>পূর্ব - দক্ষিণ</v>
+        <v>অধিক সেচ</v>
       </c>
       <c r="E72" t="str">
-        <v>উত্তর - পশ্চিম</v>
+        <v>নিবিড় চাষ</v>
       </c>
       <c r="F72" t="str">
         <v>B</v>
@@ -1841,219 +1841,219 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>নিচের কোনটি খাটো দিবা দৈর্ঘ্যের ফসল?</v>
+        <v>কোন মৃত্তিকার উৎপাদন ক্ষমতা সবচেয়ে বেশি?</v>
       </c>
       <c r="B73" t="str">
-        <v>বাঁধাকপি</v>
+        <v>বেলে</v>
       </c>
       <c r="C73" t="str">
-        <v>ফুলকপি</v>
+        <v>পলি</v>
       </c>
       <c r="D73" t="str">
-        <v>পালংশাক</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="E73" t="str">
-        <v>ঝিঙ্গা</v>
+        <v>এঁটেল-দোআঁশ</v>
       </c>
       <c r="F73" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>বোরো ধান, সরিষা, মুলা ইত্যাদি কোন ঋতুর ফসল? [ বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>হিউমিফিকেশন ও পডজোলাইজেশন প্রক্রিয়ার সময় নিচের কোন জৈব এসিড তৈরি হয়</v>
       </c>
       <c r="B74" t="str">
-        <v>রবি</v>
+        <v>এসকরবিক এসিড</v>
       </c>
       <c r="C74" t="str">
-        <v>খরিফ</v>
+        <v>ফরমিক এসিড</v>
       </c>
       <c r="D74" t="str">
-        <v>বর্ষা</v>
+        <v>টারটারিক এসিড</v>
       </c>
       <c r="E74" t="str">
-        <v>হেমন্ত</v>
+        <v>সবগুলোই</v>
       </c>
       <c r="F74" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>মাঠ ফসল নিচের কোনটি দ্বারা বেশি প্রভাবিত হয়? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ, কুমিল্লা ]</v>
+        <v>নিচের কোন ফসলটির সেচের চাহিদা সবচেয়ে কম</v>
       </c>
       <c r="B75" t="str">
-        <v>আর্দ্রতা</v>
+        <v>সরিষা</v>
       </c>
       <c r="C75" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>গোলআলু</v>
       </c>
       <c r="D75" t="str">
-        <v>কুয়াশা</v>
+        <v>ধান</v>
       </c>
       <c r="E75" t="str">
-        <v>জলপাত</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="F75" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>বড় দিবা-দৈর্ঘ্যের উদ্ভিদ কোনটি?</v>
+        <v>SRI পদ্ধতিতে বীজের অঙ্কুরোদগমের হার শতকরা কত হতে হয় ?</v>
       </c>
       <c r="B76" t="str">
-        <v>তামাক</v>
+        <v>৮৫-৭৫</v>
       </c>
       <c r="C76" t="str">
-        <v>মুলা</v>
+        <v>৭৫-৮০</v>
       </c>
       <c r="D76" t="str">
-        <v>সূর্যমুখী</v>
+        <v>৭০-৭৫</v>
       </c>
       <c r="E76" t="str">
-        <v>পাট</v>
+        <v>৮০-৮৫</v>
       </c>
       <c r="F76" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>অতি অল্প বৃষ্টিপাত অঞ্চলে কোন উদ্ভিদ ভালো জন্মে? [ কুমিল্লা সিটি কলেজ, কুমিল্লা ]</v>
+        <v>pH স্কেলের মান কত?</v>
       </c>
       <c r="B77" t="str">
-        <v>ক্যাকটাস</v>
+        <v>০-১৪</v>
       </c>
       <c r="C77" t="str">
-        <v>চিরহরিৎ</v>
+        <v>১-১৪</v>
       </c>
       <c r="D77" t="str">
-        <v>পাতাঝরা</v>
+        <v>১-১৬</v>
       </c>
       <c r="E77" t="str">
-        <v>সরলবর্গীয়</v>
+        <v>১-১৭</v>
       </c>
       <c r="F77" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>রাজশাহীর লালপুরে বার্ষিক গড় বৃষ্টিপাত কত?</v>
+        <v>সবুজ সার তৈরিতে ব্যবহৃত গাছ- i. ধৈঞ্চা ii. ধান iii. শণপাট নিচের কোনটি সঠিক?</v>
       </c>
       <c r="B78" t="str">
-        <v>৮০ সে.মি</v>
+        <v>i ও ii</v>
       </c>
       <c r="C78" t="str">
-        <v>১০০ সে.মি</v>
+        <v>ii ও iii</v>
       </c>
       <c r="D78" t="str">
-        <v>১২ সে.মি.</v>
+        <v>i ও iii</v>
       </c>
       <c r="E78" t="str">
-        <v>১৯৮ সে.মি.</v>
+        <v>i, ii ও iii</v>
       </c>
       <c r="F78" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>গাছ তার প্রাপ্ত আলোর কত ভাগ সালোকসংশ্লেষণে ব্যবহার করে?</v>
+        <v>মালচিং এর মাধ্যমে মাটির কী নিয়ন্ত্রণ করা হয়?</v>
       </c>
       <c r="B79" t="str">
-        <v>১%</v>
+        <v>তাপমাত্রা</v>
       </c>
       <c r="C79" t="str">
-        <v>২%</v>
+        <v>আর্দ্রতা</v>
       </c>
       <c r="D79" t="str">
-        <v>৫%</v>
+        <v>পুষ্টি সরবরাহ</v>
       </c>
       <c r="E79" t="str">
-        <v>১০%</v>
+        <v>বায়ু চলাচল</v>
       </c>
       <c r="F79" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>বাংলাদেশে শীতকালে সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>বাংলাদেশের কোন অঞ্চলের মাটি মূলত ক্ষারীয়?</v>
       </c>
       <c r="B80" t="str">
-        <v>২০° - ৩০° সে.</v>
+        <v>পাহাড়ি</v>
       </c>
       <c r="C80" t="str">
-        <v>২৪° - ২৮° সে.</v>
+        <v>সমতল</v>
       </c>
       <c r="D80" t="str">
-        <v>১৮° - ২৫° সে.</v>
+        <v>উপকূলীয়</v>
       </c>
       <c r="E80" t="str">
-        <v>২৬° - ৩২°  সে.</v>
+        <v>মাঝারি উঁচু</v>
       </c>
       <c r="F80" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>নিচের কোনটি খরা সহিষ্ণু ধানের জাত? [সরকারি শহীদ বুলবুল কলেজ, পাবনা।]</v>
+        <v>জমিতে পানি সেচের প্রয়োজন হয় কেন?</v>
       </c>
       <c r="B81" t="str">
-        <v>বি আর-৫৭</v>
+        <v>এঁটেল বুনট তৈরি করা</v>
       </c>
       <c r="C81" t="str">
-        <v>বি আর-২১</v>
+        <v>জৈব পদার্থের পচন রোধ করা</v>
       </c>
       <c r="D81" t="str">
-        <v>মুক্তা</v>
+        <v>অণুজীবের কার্যাবলি বৃদ্ধি করা</v>
       </c>
       <c r="E81" t="str">
-        <v>চান্দিনা</v>
+        <v>মাটির আর্দ্রতা কমানো</v>
       </c>
       <c r="F81" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>বাংলাদেশের জলবায়ুর ধরন কেমন?</v>
+        <v>জমির লবণাক্ততা দূরীকরণে কোনটি ব্যবহার করা যায়?</v>
       </c>
       <c r="B82" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>সালফার</v>
       </c>
       <c r="C82" t="str">
-        <v>চরম ভাবাপন্ন</v>
+        <v>জিপসাম</v>
       </c>
       <c r="D82" t="str">
-        <v>নিরক্ষীয়</v>
+        <v>ক্যালসাইট</v>
       </c>
       <c r="E82" t="str">
-        <v>উষ্ণমণ্ডলীয়</v>
+        <v>ট্রাইকোডামা</v>
       </c>
       <c r="F82" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>বাংলাদেশের গ্রীষ্মকালে কোন মৌসুমি বায়ুর প্রভাবে বৃষ্টিপাত হয়? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>কোন সেচ পদ্ধতিতে ভূমিক্ষয় বেশি হয়?</v>
       </c>
       <c r="B83" t="str">
-        <v>উত্তর-পশ্চিম</v>
+        <v>ফোয়ারা</v>
       </c>
       <c r="C83" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>প্লাবন</v>
       </c>
       <c r="D83" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>বৃত্তাকার সেচ</v>
       </c>
       <c r="E83" t="str">
-        <v>উত্তর-পূর্ব</v>
+        <v>ড্রিপ সেচ</v>
       </c>
       <c r="F83" t="str">
         <v>B</v>
@@ -2061,99 +2061,99 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>সূর্য উদয় থেকে অস্ত যাওয়া পর্যন্ত সময়কে কী বলে?</v>
+        <v>ভূমিক্ষয় রোধে সর্বাপেক্ষা কার্যকর উপায় কোনটি?</v>
       </c>
       <c r="B84" t="str">
-        <v>সূর্য বিকিরণ</v>
+        <v>আচ্ছাদন ফসলের চাষ</v>
       </c>
       <c r="C84" t="str">
-        <v>সূর্যালোক</v>
+        <v>জমিতে আইল বাধাঁ</v>
       </c>
       <c r="D84" t="str">
-        <v>সৌরশক্তি</v>
+        <v>জাবড়া প্রয়োগ</v>
       </c>
       <c r="E84" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>গাছ লাগনো</v>
       </c>
       <c r="F84" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ধানের অভিযোজনের জন্য সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>মাটির কোন কণা সবচেয়ে সূক্ষ্ম ?</v>
       </c>
       <c r="B85" t="str">
-        <v>২০°সে.</v>
+        <v>বেলে</v>
       </c>
       <c r="C85" t="str">
-        <v>৩০° সে.</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D85" t="str">
-        <v>৪০° সে.</v>
+        <v>পলি</v>
       </c>
       <c r="E85" t="str">
-        <v>৪৫° সে.</v>
+        <v>কর্দম</v>
       </c>
       <c r="F85" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>বড় দিনের উদ্ভিদে কত ঘণ্টার বেশি আলো প্রয়োজন? [শাহজালাল সিটি কলেজ, সিলেট।]</v>
+        <v>কোন মাটিতে সব কণার অনুপাত সমান থাকে?</v>
       </c>
       <c r="B86" t="str">
-        <v>১১</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="C86" t="str">
-        <v>১২</v>
+        <v>পলি মাটি</v>
       </c>
       <c r="D86" t="str">
-        <v>৯</v>
+        <v>বেলে</v>
       </c>
       <c r="E86" t="str">
-        <v>৬</v>
+        <v>এঁটেল মাটি</v>
       </c>
       <c r="F86" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>কোনটি বড় দিনের উদ্ভিদ নয়?</v>
+        <v>নিচের অনুচ্ছেদটি পড় এবং প্রশ্নের উত্তর দাও: আসিফ তার মা-বাবার সাথে রাঙ্গামাটি পার্বত্য জেলায় বেড়াতে গেলে পথে সে দেখল যে ফসলের জমিতে ছোট নদীর মতো তৈরি হয়েছে। সে এ ধরনের ভূমিক্ষয় সংরক্ষণের উপায় নিয়ে চিন্তা করল। [খুলনা সরকারি মডেল স্কুল এন্ড কলেজ] Q. আসিফ কোন ধরনের ভূমিক্ষয় দেখেছিল?</v>
       </c>
       <c r="B87" t="str">
-        <v>আউশ ধান</v>
+        <v>নালা</v>
       </c>
       <c r="C87" t="str">
-        <v>পাট</v>
+        <v>আস্তরণ</v>
       </c>
       <c r="D87" t="str">
-        <v>চাল কুমড়া</v>
+        <v>রিল</v>
       </c>
       <c r="E87" t="str">
-        <v>সরিষা</v>
+        <v>নদী ভাঙন</v>
       </c>
       <c r="F87" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>নিচের কোনটি স্বল্প দিবসী উদ্ভিদ?</v>
+        <v>মৃত্তিকা দ্রবণের pH কত হলে উভয় লিটমাস কাগজের রং অপরিবর্তিত থাকে?</v>
       </c>
       <c r="B88" t="str">
-        <v>বেগুন</v>
+        <v>৬</v>
       </c>
       <c r="C88" t="str">
-        <v>শণপাট</v>
+        <v>৭</v>
       </c>
       <c r="D88" t="str">
-        <v>টমেটো</v>
+        <v>৮</v>
       </c>
       <c r="E88" t="str">
-        <v>আখ</v>
+        <v>৯</v>
       </c>
       <c r="F88" t="str">
         <v>B</v>
@@ -2161,79 +2161,79 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>বাংলাদেশে কোন মাসে অধিক বৃষ্টিপাত হয়? [হাজী লালমিয়া সিটি বিশ্ববিদ্যালয় কলেজ, গোপালগঞ্জ ]</v>
+        <v>রাতুলের ফসলী জমির ফলন বৃদ্ধির কারণ কী?</v>
       </c>
       <c r="B89" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>সোপান চাষ অনুসরণ</v>
       </c>
       <c r="C89" t="str">
-        <v>জুলাই-আগস্ট</v>
+        <v>শস্য পঞ্জিকা অনুসরণ</v>
       </c>
       <c r="D89" t="str">
-        <v>জানুয়ারি-ফেব্রুয়ারি</v>
+        <v>শস্য পর্যায় অবলম্বন</v>
       </c>
       <c r="E89" t="str">
-        <v>নভেম্বর-ডিসেম্বর</v>
+        <v>ফালিবদ্ধ চাষ অনুসরণ</v>
       </c>
       <c r="F89" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>খাটোদিবসী উদ্ভিদ কোনটি? [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
+        <v>পানি সেচের সবচেয়ে স্থায়ী ও সহজ পদ্ধতি কোনটি?</v>
       </c>
       <c r="B90" t="str">
-        <v>মুলা</v>
+        <v>AWD</v>
       </c>
       <c r="C90" t="str">
-        <v>ছোলা</v>
+        <v>নালা</v>
       </c>
       <c r="D90" t="str">
-        <v>আলু</v>
+        <v>ফোয়ারা</v>
       </c>
       <c r="E90" t="str">
-        <v>সয়াবিন</v>
+        <v>বৃত্তাকার</v>
       </c>
       <c r="F90" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>তাপমাত্রার বৃদ্ধি আলু উৎপাদনে কী প্রভাব ফেলে? [খুলনা পাবলিক কলেজ, খুলনা ]</v>
+        <v>কোন পদ্ধতিতে সমস্ত জমিকে চাল অনুযায়ী কয়েকটি খন্ডে ভাগ করে সেচ দেওয়া হয়?</v>
       </c>
       <c r="B91" t="str">
-        <v>উৎপাদন বৃদ্ধি পায়</v>
+        <v>নালা</v>
       </c>
       <c r="C91" t="str">
-        <v>পোকার আক্রমণ বেড়ে যায়</v>
+        <v>চেক বেসিন</v>
       </c>
       <c r="D91" t="str">
-        <v>উৎপাদন হ্রাস পায়</v>
+        <v>ড্রিপ</v>
       </c>
       <c r="E91" t="str">
-        <v>অঙ্কুরোদগম বাধাগ্রস্ত হয়</v>
+        <v>রিং বেসিন</v>
       </c>
       <c r="F91" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>নিচের কোনটি ছায়াতে ভালো জন্মে?</v>
+        <v>কোন জমিতে সেচ পদ্ধতি নিচের কোনটির ওপর নির্ভর করে?</v>
       </c>
       <c r="B92" t="str">
-        <v>ধান</v>
+        <v>ফসলের উৎপাদন মৌসুম</v>
       </c>
       <c r="C92" t="str">
-        <v>গম</v>
+        <v>মাটির জৈব পদার্থের উপস্থিতি</v>
       </c>
       <c r="D92" t="str">
-        <v>পান</v>
+        <v>ভূমির বন্ধুরতা</v>
       </c>
       <c r="E92" t="str">
-        <v>ভুট্টা</v>
+        <v>সার ব্যবহারের সময়ের ওপর</v>
       </c>
       <c r="F92" t="str">
         <v>C</v>
@@ -2241,39 +2241,39 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ছোট দিনের উদ্ভিদের ফল ধারণের জন্য কত ঘণ্টার কম আলো লাগে?</v>
+        <v>ভূমিক্ষয়ের কারণ কোনটি? [ইবনে তাইমিয়া স্কুল এন্ড কলেজ, কুমিল্লা]</v>
       </c>
       <c r="B93" t="str">
-        <v>১৬ ঘণ্টা</v>
+        <v>ভূমির ঢাল</v>
       </c>
       <c r="C93" t="str">
-        <v>১৪ ঘণ্টা</v>
+        <v>শস্য পর্যায়</v>
       </c>
       <c r="D93" t="str">
-        <v>১৩ ঘণ্টা</v>
+        <v>জৈব পদার্থ</v>
       </c>
       <c r="E93" t="str">
-        <v>১২ ঘণ্টা</v>
+        <v>চাষাবাদ</v>
       </c>
       <c r="F93" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>বীজের অঙ্কুরোদগম উপযোগী তাপমাত্রা কত?</v>
+        <v>জমির ঢাল বরাবর ক্ষয়রেখা সৃষ্টি হয় কোন ধরনের ভূমিক্ষয়ের ফলে?</v>
       </c>
       <c r="B94" t="str">
-        <v>১৫° সে.</v>
+        <v>অন্তরণ</v>
       </c>
       <c r="C94" t="str">
-        <v>২০° সে.</v>
+        <v>রিল</v>
       </c>
       <c r="D94" t="str">
-        <v>২৫° সে.</v>
+        <v>গালি</v>
       </c>
       <c r="E94" t="str">
-        <v>৩০° সে.</v>
+        <v>পাত</v>
       </c>
       <c r="F94" t="str">
         <v>C</v>
@@ -2281,39 +2281,39 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>কোনটি গ্রীষ্ম মৌসুমের ফসল?</v>
+        <v>অম্লমান অনুসারে মাটিকে কয় ভাগে ভাগ করা হয়?</v>
       </c>
       <c r="B95" t="str">
-        <v>বোরো ধান</v>
+        <v>২</v>
       </c>
       <c r="C95" t="str">
-        <v>গম</v>
+        <v>৩</v>
       </c>
       <c r="D95" t="str">
-        <v>সয়াবিন</v>
+        <v>৪</v>
       </c>
       <c r="E95" t="str">
-        <v>পেঁয়াজ</v>
+        <v>৫</v>
       </c>
       <c r="F95" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>আবহাওয়া নিচের কোনটির ওপর বেশি প্রভাব ফেলে? [অমৃত লাল দে মহাবিদ্যালয়, বরিশাল। ]</v>
+        <v>প্রশম বা নিরপেক্ষ মাটির অম্লমান (pH) কোনটি।</v>
       </c>
       <c r="B96" t="str">
-        <v>দিনের দৈর্ঘ্য</v>
+        <v>৭ এর কম</v>
       </c>
       <c r="C96" t="str">
-        <v>মোট সূর্যালোক ঘণ্টা</v>
+        <v>৭</v>
       </c>
       <c r="D96" t="str">
-        <v>সৌরশক্তি</v>
+        <v>৭ এর বেশি</v>
       </c>
       <c r="E96" t="str">
-        <v>সৌর বিকিরণ</v>
+        <v>৮ এর বেশি</v>
       </c>
       <c r="F96" t="str">
         <v>B</v>
@@ -2321,79 +2321,79 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>উদ্ভিদের প্রস্বেদন কখন কমে যায়? [ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, রংপুর ]</v>
+        <v>বাংলাদেশের কোন অঞ্চলে গালি ভূমিক্ষয় বেশি দেখা যায়?</v>
       </c>
       <c r="B97" t="str">
-        <v>বায়ুমণ্ডলের তাপমাত্রা বৃদ্ধি পেলে</v>
+        <v>পার্বত্য</v>
       </c>
       <c r="C97" t="str">
-        <v>দিবা দৈর্ঘ্য হ্রাস পেলে</v>
+        <v>উপকূলীয়</v>
       </c>
       <c r="D97" t="str">
-        <v>বায়ুতে জলীয়বাষ্প বেশি থাকলে</v>
+        <v>প্লাবন</v>
       </c>
       <c r="E97" t="str">
-        <v>বৃষ্টিপাত কম হলে</v>
+        <v>বরেন্দ্র</v>
       </c>
       <c r="F97" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>কোনটি ছোট দিনের উদ্ভিদ নয়? [পটুয়াখালী সরকারি মহিলা কলেজ, পটুয়াখালী।]</v>
+        <v>আন্তর্জাতিক ও যুক্তরাষ্ট্র পদ্ধতিতে মাটির বুনটকে কয় শ্রেণিতে ভাগ করা যায়?</v>
       </c>
       <c r="B98" t="str">
-        <v>গম</v>
+        <v>৯</v>
       </c>
       <c r="C98" t="str">
-        <v>সরিষা</v>
+        <v>১১</v>
       </c>
       <c r="D98" t="str">
-        <v>গিমা</v>
+        <v>১২</v>
       </c>
       <c r="E98" t="str">
-        <v>টমেটো</v>
+        <v>১৪</v>
       </c>
       <c r="F98" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>কোন মৌসুমি বায়ুর প্রভাবে বাংলাদেশে কালবৈশাখী হয়?</v>
+        <v>বৃষ্টির ফোঁটা কত মাইল বেগে পড়লে সেখানের মাটি আলগা হয়ে চারদিকে ছিটিয়ে যায়?</v>
       </c>
       <c r="B99" t="str">
-        <v>দক্ষিণ -পশ্চিম</v>
+        <v>১০ মাইল</v>
       </c>
       <c r="C99" t="str">
-        <v>উত্তর -পশ্চিম</v>
+        <v>২০ মাইল</v>
       </c>
       <c r="D99" t="str">
-        <v>দক্ষিণ - পূর্ব</v>
+        <v>২২ মাইল</v>
       </c>
       <c r="E99" t="str">
-        <v>উত্তর - পূর্ব</v>
+        <v>২৪ মাইল</v>
       </c>
       <c r="F99" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>অধিক তাপমাত্রা ও বৃষ্টিপাতের অঞ্চলে নিচের কোন উদ্ভিদ জন্মে?</v>
+        <v>নিচের কোনটি নিরপেক্ষ বা প্রশম মাটির pH?</v>
       </c>
       <c r="B100" t="str">
-        <v>ক্যাকটাস</v>
+        <v>০.০</v>
       </c>
       <c r="C100" t="str">
-        <v>চিরহরিৎ</v>
+        <v>৭.০</v>
       </c>
       <c r="D100" t="str">
-        <v>সরলবর্গীয়</v>
+        <v>৬.০</v>
       </c>
       <c r="E100" t="str">
-        <v>পাতাঝরা</v>
+        <v>৮.০</v>
       </c>
       <c r="F100" t="str">
         <v>B</v>
@@ -2401,39 +2401,39 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>খরিপ-২ ঋতুর ফসল কোনটি?</v>
+        <v>নিচের কোনটি পানি ভূমিক্ষয়ের উদাহরণ?</v>
       </c>
       <c r="B101" t="str">
-        <v>আউশ ধান</v>
+        <v>সেলটেশন</v>
       </c>
       <c r="C101" t="str">
-        <v>আমন ধান</v>
+        <v>লম্ফ ক্ষয়</v>
       </c>
       <c r="D101" t="str">
-        <v>মিষ্টি আলু</v>
+        <v>গালি ভূমিক্ষয়</v>
       </c>
       <c r="E101" t="str">
-        <v>মসুর</v>
+        <v>বায়ুপ্রবাহ</v>
       </c>
       <c r="F101" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>রবি ঋতুর বৈশিষ্ট্য কোনটি?</v>
+        <v>কোন মাটিতে সব কণার অনুপাত সমান থাকে?</v>
       </c>
       <c r="B102" t="str">
-        <v>দিনবড় রাত ছোট</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="C102" t="str">
-        <v>বাতাসে আর্দ্রতা বেশি</v>
+        <v>পলি মাটি</v>
       </c>
       <c r="D102" t="str">
-        <v>তাপমাত্রা বেশি থাকে</v>
+        <v>বেলে</v>
       </c>
       <c r="E102" t="str">
-        <v>তাপমাত্রা কম থাকে</v>
+        <v>এঁটেল মাটি</v>
       </c>
       <c r="F102" t="str">
         <v>D</v>
@@ -2441,39 +2441,39 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>গমের অংকুরোদগমের সর্বোত্তম তাপমাত্রা কত? [কুমিল্লা সিটি কলেজ, কুমিল্লা ]</v>
+        <v>অল্প মাটির pH মান কত?</v>
       </c>
       <c r="B103" t="str">
-        <v>১৫°C</v>
+        <v>৭.০০</v>
       </c>
       <c r="C103" t="str">
-        <v>১৭°C</v>
+        <v>৫.৫</v>
       </c>
       <c r="D103" t="str">
-        <v>১৯°C</v>
+        <v>৮.৫</v>
       </c>
       <c r="E103" t="str">
-        <v>২২.৫°C</v>
+        <v>১০.৫</v>
       </c>
       <c r="F103" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ঢল বন্যা হয় কখন?</v>
+        <v>অম্লীয় মৃত্তিকায় কোন ফসল ভালো হয়?</v>
       </c>
       <c r="B104" t="str">
-        <v>এপ্রিল - মে</v>
+        <v>আনারস</v>
       </c>
       <c r="C104" t="str">
-        <v>মার্চ – এপ্রিল</v>
+        <v>নারিকেল</v>
       </c>
       <c r="D104" t="str">
-        <v>মে - জুন</v>
+        <v>তাল</v>
       </c>
       <c r="E104" t="str">
-        <v>মে - জুলাই</v>
+        <v>খেজুর</v>
       </c>
       <c r="F104" t="str">
         <v>A</v>
@@ -2481,39 +2481,39 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>খরা সহনশীল ফসল কোনটি? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ]</v>
+        <v>SRI পদ্ধতিতে কতদিন বয়সের ধানের চারা রোপণ করতে হয়?</v>
       </c>
       <c r="B105" t="str">
-        <v>তিল</v>
+        <v>১০-১৫ দিন</v>
       </c>
       <c r="C105" t="str">
-        <v>গম</v>
+        <v>১৫-২০ দিন</v>
       </c>
       <c r="D105" t="str">
-        <v>মসুর ডাল</v>
+        <v>২০-২৫ দিন</v>
       </c>
       <c r="E105" t="str">
-        <v>ধান</v>
+        <v>২৫-৩০ দিন</v>
       </c>
       <c r="F105" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>কয় ধরনের আলোক সংবেদনশীল উদ্ভিদ আছে?</v>
+        <v>SRI পদ্ধতিতে ধান চাষ করলে ধানের ফলন শতকরা কত ভাগ বৃদ্ধি পায়?</v>
       </c>
       <c r="B106" t="str">
-        <v>২ ধরনের</v>
+        <v>১০</v>
       </c>
       <c r="C106" t="str">
-        <v>৪ ধরনের</v>
+        <v>১৫</v>
       </c>
       <c r="D106" t="str">
-        <v>৬ ধরনের</v>
+        <v>২০</v>
       </c>
       <c r="E106" t="str">
-        <v>৮ ধরনের</v>
+        <v>২৫</v>
       </c>
       <c r="F106" t="str">
         <v>B</v>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>দিবা দৈর্ঘ্য হ্রাস বৃদ্ধির কারণ কোনটি? [নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>অম্লসহনশীল ফসল কোনটি</v>
       </c>
       <c r="B107" t="str">
-        <v>পৃথিবীর আকার</v>
+        <v>সরিষা</v>
       </c>
       <c r="C107" t="str">
-        <v>পৃথিবীর পরিধি</v>
+        <v>তুলা</v>
       </c>
       <c r="D107" t="str">
-        <v>পৃথিবীর ঘূর্ণন</v>
+        <v>চা</v>
       </c>
       <c r="E107" t="str">
-        <v>সূর্যের দূরত্ব</v>
+        <v>টমেটো</v>
       </c>
       <c r="F107" t="str">
         <v>C</v>
@@ -2541,39 +2541,39 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>রবি মৌসুমের সময়কাল কোনটি?</v>
+        <v>কোন মাটির পানি ধারণ ক্ষমতা সবচেয়ে বেশি?</v>
       </c>
       <c r="B108" t="str">
-        <v>নভেম্বর-ফেব্রুয়ারি</v>
+        <v>দোআঁশ বেলে</v>
       </c>
       <c r="C108" t="str">
-        <v>মার্চ-জুন</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D108" t="str">
-        <v>জানুয়ারি-এপ্রিল</v>
+        <v>পলি</v>
       </c>
       <c r="E108" t="str">
-        <v>জুলাই-সেপ্টেম্বর</v>
+        <v>এঁটেল</v>
       </c>
       <c r="F108" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>শীতকালীন শাকসবজি চাষের উপযোগী তাপমাত্রা কত? [ নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>মাটির উর্বরতা বৃদ্ধির জন্য যেসকল জৈব পদার্থ দিতে হয়- i. পচা আবর্জনা ii. গোবর iii. ইউরিয়া নিচের কোনটি সঠিক?</v>
       </c>
       <c r="B109" t="str">
-        <v>২৫-৩০°</v>
+        <v>i ও ii</v>
       </c>
       <c r="C109" t="str">
-        <v>২০-২৫°</v>
+        <v>ii ও iii</v>
       </c>
       <c r="D109" t="str">
-        <v>১৫-২০°</v>
+        <v>i ও iii</v>
       </c>
       <c r="E109" t="str">
-        <v>১০-১৫°</v>
+        <v>i, ii ও iii</v>
       </c>
       <c r="F109" t="str">
         <v>A</v>
@@ -2581,99 +2581,99 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>বায়ুমন্ডলে গ্রিনহাউজ গ্যাস বৃদ্ধির কারণ কী? [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর]</v>
+        <v>শিম জাতীয় শস্য চাষ করলে কোনটি সংযোজন হয়? [পটুয়াখালী সরকারি মহিলা কলেজ, পটুয়াখালী]</v>
       </c>
       <c r="B110" t="str">
-        <v>বৃক্ষরোপণ</v>
+        <v>অক্সিজেন</v>
       </c>
       <c r="C110" t="str">
-        <v>বৃক্ষ নিধন</v>
+        <v>হাইড্রোজেন</v>
       </c>
       <c r="D110" t="str">
-        <v>মৎস্য চাষ</v>
+        <v>নাইট্রোজেন</v>
       </c>
       <c r="E110" t="str">
-        <v>হাঁস-মুরগি পালন</v>
+        <v>কার্বন ডাইঅক্সাইড</v>
       </c>
       <c r="F110" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ফসল উৎপাদনের সুবিধার্থে সারা বছরকে কয়টি মৌসুমে ভাগ করা হয়েছে?</v>
+        <v>মাটির অম্লত্ব প্রকাশের একক কোনটি?</v>
       </c>
       <c r="B111" t="str">
-        <v>২</v>
+        <v>pH</v>
       </c>
       <c r="C111" t="str">
-        <v>৩</v>
+        <v>EH</v>
       </c>
       <c r="D111" t="str">
-        <v>৪</v>
+        <v>EC</v>
       </c>
       <c r="E111" t="str">
-        <v>৫</v>
+        <v>CEC</v>
       </c>
       <c r="F111" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>পৃথিবীকে কতটি অঞ্চলে ভাগ করা হয়েছে?</v>
+        <v>নিচের অনুচ্ছেদটি পড় এবং প্রশ্নের উত্তর দাও: আসিফ তার মা-বাবার সাথে রাঙ্গামাটি পার্বত্য জেলায় বেড়াতে গেলে পথে সে দেখল যে ফসলের জমিতে ছোট নদীর মতো তৈরি হয়েছে। সে এ ধরনের ভূমিক্ষয় সংরক্ষণের উপায় নিয়ে চিন্তা করল। [খুলনা সরকারি মডেল স্কুল এন্ড কলেজ] Q. আসিফের চিন্তা করা উপায়ের মধ্যে ছিল- i. কন্টুর চাষ ii. জৈব পদার্থ প্রয়োগ ii. বায়ুর দিক পরিবর্তন নিচের কোনটি সঠিক?</v>
       </c>
       <c r="B112" t="str">
-        <v>২টি</v>
+        <v>i</v>
       </c>
       <c r="C112" t="str">
-        <v>৪টি</v>
+        <v>i ও ii</v>
       </c>
       <c r="D112" t="str">
-        <v>৬টি</v>
+        <v>ii ও iii</v>
       </c>
       <c r="E112" t="str">
-        <v>৮টি</v>
+        <v>i, ii ও iii</v>
       </c>
       <c r="F112" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>বাংলাদেশে শীতকালে সর্বনিম্ন তাপমাত্রা কত?</v>
+        <v>কোন মাটির কণা সবচেয়ে ছোট?</v>
       </c>
       <c r="B113" t="str">
-        <v>৫° - ১৫° সে</v>
+        <v>বেলে</v>
       </c>
       <c r="C113" t="str">
-        <v>৭° - ১৫° সে.</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D113" t="str">
-        <v>৯° - ১৮° সে.</v>
+        <v>পলি</v>
       </c>
       <c r="E113" t="str">
-        <v>১০°-১৫° সে.</v>
+        <v>কর্দম</v>
       </c>
       <c r="F113" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ভূপৃষ্ঠের উপর বায়ু যে বল প্রয়োগ করে তাকে বলে- [সোনার বাংলা কলেজ, কুমিল্লা।]</v>
+        <v>পাহাড়ি ঢালে ফসল ব্যবস্থাপনায় কয়েক সারি শস্যের অন্তর জমির ঢালে আড়াআড়িভাবে ঘন ঘাস বা শস্যের চাষকে কী বলে?</v>
       </c>
       <c r="B114" t="str">
-        <v>বায়ুর চাপ</v>
+        <v>স্ট্রিপ ক্রপিং</v>
       </c>
       <c r="C114" t="str">
-        <v>বায়ুপ্রবাহ</v>
+        <v>ইন্টার ক্রপিং</v>
       </c>
       <c r="D114" t="str">
-        <v>বায়ুর দিক</v>
+        <v>মিক্স ক্রপিং</v>
       </c>
       <c r="E114" t="str">
-        <v>বায়ুর তাপমাত্রা</v>
+        <v>রগিং</v>
       </c>
       <c r="F114" t="str">
         <v>A</v>
@@ -2681,59 +2681,59 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>শস্যের সার্বিক বৃদ্ধির জন্য নিচের কোনটি সবচেয়ে বেশি ভূমিকা রাখে? [শহীদ বুলবুল সরকারি কলেজ, পাবনা।]</v>
+        <v>ভূমিক্ষয় রোধ করার উপায়?</v>
       </c>
       <c r="B115" t="str">
-        <v>আলো</v>
+        <v>মালচিং</v>
       </c>
       <c r="C115" t="str">
-        <v>তাপমাত্রা</v>
+        <v>পশুচারণ</v>
       </c>
       <c r="D115" t="str">
-        <v>বৃষ্টি</v>
+        <v>জুমচাষ</v>
       </c>
       <c r="E115" t="str">
-        <v>খরা</v>
+        <v>পানি প্রবাহ</v>
       </c>
       <c r="F115" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>উত্তর-পূর্ব দিক দিয়ে মৌসুমি বায়ু প্রবাহিত হয় কোন ঋতুতে?</v>
+        <v>কোন এসিড বিয়োজিত হয়ে বাইকার্বনেট ও হাইড্রোজেন আয়ন সৃষ্টি হয়?</v>
       </c>
       <c r="B116" t="str">
-        <v>গ্রীষ্ম</v>
+        <v>সালফিউরিক</v>
       </c>
       <c r="C116" t="str">
-        <v>বর্ষা</v>
+        <v>কার্বনিক</v>
       </c>
       <c r="D116" t="str">
-        <v>শরৎ</v>
+        <v>নাইট্রিক</v>
       </c>
       <c r="E116" t="str">
-        <v>শীত</v>
+        <v>কার্বন ডাইঅক্সাইড</v>
       </c>
       <c r="F116" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>কোনটি শীতকালীন ফসল?</v>
+        <v>যদি কোনো মাটিতে প্রায় ৫০% বালি এবং ৫০% পলি ও কর্দম কণা থাকে, তবে তাকে কী মাটি বলে?</v>
       </c>
       <c r="B117" t="str">
-        <v>সয়াবিন</v>
+        <v>দোআঁশ বেলে</v>
       </c>
       <c r="C117" t="str">
-        <v>ছোলা</v>
+        <v>দোআঁশ</v>
       </c>
       <c r="D117" t="str">
-        <v>জোয়ার</v>
+        <v>বেলে এঁটেল</v>
       </c>
       <c r="E117" t="str">
-        <v>সরগম</v>
+        <v>পলি এঁটেল</v>
       </c>
       <c r="F117" t="str">
         <v>B</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>শীতকালে বাংলাদেশে দিবা-দৈর্ঘ্য সাধারণত কত ঘণ্টা হয়?</v>
+        <v>এঁটেল মাটিকে দো-আঁশ মাটিতে পরিণত করতে বালু, পলি ও কর্দম কণার অনুপাত কত?</v>
       </c>
       <c r="B118" t="str">
-        <v>১০-১১ ঘণ্টা</v>
+        <v>২ঃ১ঃ১</v>
       </c>
       <c r="C118" t="str">
-        <v>১১-১২ ঘণ্টা</v>
+        <v>৩ঃ২ঃ১</v>
       </c>
       <c r="D118" t="str">
-        <v>১২-১৩ ঘণ্টা</v>
+        <v>১ঃ২ঃ১</v>
       </c>
       <c r="E118" t="str">
-        <v>১০-১২ ঘণ্টা</v>
+        <v>১ : ১ : ২</v>
       </c>
       <c r="F118" t="str">
         <v>A</v>
@@ -2761,139 +2761,139 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>কোনটি দিন নিরপেক্ষ উদ্ভিদ? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>প্রাকৃতিক ভূমিক্ষয়ের কারণ কোনটি?</v>
       </c>
       <c r="B119" t="str">
-        <v>পেয়ারা</v>
+        <v>ভূমিকৰ্ষণ</v>
       </c>
       <c r="C119" t="str">
-        <v>সূর্যমুখী</v>
+        <v>জুমচাষ</v>
       </c>
       <c r="D119" t="str">
-        <v>ডালিয়া</v>
+        <v>পাহাড় কাটা</v>
       </c>
       <c r="E119" t="str">
-        <v>গোলাপ</v>
+        <v>পানি প্রবাহ</v>
       </c>
       <c r="F119" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ডালিয়া, চন্দ্রমল্লিকা কী দিনের উদ্ভিদ? [বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>ভূমিক্ষয় রোধে সর্বাপেক্ষা কার্যকর উপায় কোনটি? [কসবা তফজ্জল আলী কলেজ, ব্রাহ্মণবাড়িয়া]</v>
       </c>
       <c r="B120" t="str">
-        <v>আলোক অসংবেদনশীল</v>
+        <v>আচ্ছাদন ফসলের চাষ</v>
       </c>
       <c r="C120" t="str">
-        <v>ছোট দিন</v>
+        <v>জমিতে আইল বাঁধা</v>
       </c>
       <c r="D120" t="str">
-        <v>বড় দিন</v>
+        <v>জাবড়া প্রয়োগ</v>
       </c>
       <c r="E120" t="str">
-        <v>দিন নিরপেক্ষ</v>
+        <v>গাছ লাগানো</v>
       </c>
       <c r="F120" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>নিচের কোনটি দিবস নিরক্ষে?</v>
+        <v>নিচের কোনটি অম্ল পছন্দকারী ফসল?</v>
       </c>
       <c r="B121" t="str">
-        <v>লেটুস</v>
+        <v>&lt;p&gt;নারিকেল &lt;/p&gt;</v>
       </c>
       <c r="C121" t="str">
-        <v>পাট</v>
+        <v>আনারস</v>
       </c>
       <c r="D121" t="str">
-        <v>মুগ</v>
+        <v>তাল</v>
       </c>
       <c r="E121" t="str">
-        <v>ফুলকপি</v>
+        <v>খেজুর</v>
       </c>
       <c r="F121" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>বাংলাদেশে কোন মাসে কুলের বাডিং করা যায়? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ ]</v>
+        <v>বৃষ্টির ফোঁটা কত মাইল বেগে পড়লে সেখানের মাটি আলগা হয়ে চারদিকে ছিটিয়ে যায়? [শহীদ পুলিশ স্মৃতি কলেজ, ঢাকা]</v>
       </c>
       <c r="B122" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>১০ মাইল</v>
       </c>
       <c r="C122" t="str">
-        <v>মে-জুন</v>
+        <v>২০ মাইল</v>
       </c>
       <c r="D122" t="str">
-        <v>জুলাই-আগস্ট</v>
+        <v>২২ মাইল</v>
       </c>
       <c r="E122" t="str">
-        <v>সেপ্টেম্বর-অক্টোবর</v>
+        <v>২৪ মাইল</v>
       </c>
       <c r="F122" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>রাতের তাপমাত্রা কত হলে ফুল ধারণ বিলম্বিত হয়? [কুমিল্লা সরকারি কলেজ, কুমিল্লা ]</v>
+        <v>বায়ুর সাথে লাফিয়ে মৃত্তিকা কণার স্থানান্তর হওয়াকে কি বলে?</v>
       </c>
       <c r="B123" t="str">
-        <v>১০° সে. এর কম</v>
+        <v>সয়েল ক্লিপ</v>
       </c>
       <c r="C123" t="str">
-        <v>১৫° সে. এর বেশি</v>
+        <v>স্প্ল্যাস ইরোসন</v>
       </c>
       <c r="D123" t="str">
-        <v>২০° সে. এর কম</v>
+        <v>সেন্টেশন</v>
       </c>
       <c r="E123" t="str">
-        <v>২০° সে. এর বেশি</v>
+        <v>শীট ইরোসন</v>
       </c>
       <c r="F123" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>উদ্ভিদজগতকে জলবায়ুর উপাদানের সংবেদনশীলতার ভিত্তিতে কতভাগে ভাগ করা যায়?</v>
+        <v>মাটির বিভিন্ন প্রকার পুষ্টি উপাদানের সহজলভ্যতা কিসের উপর নির্ভর করে?</v>
       </c>
       <c r="B124" t="str">
-        <v>২ ভাগে</v>
+        <v>মাটির উর্বরতা</v>
       </c>
       <c r="C124" t="str">
-        <v>৩ ভাগে</v>
+        <v>মাটির ক্ষারত্বের তীব্রতা</v>
       </c>
       <c r="D124" t="str">
-        <v>৪ ভাগে</v>
+        <v>মাটির অম্লত্বের তীব্রতা</v>
       </c>
       <c r="E124" t="str">
-        <v>৫ ভাগে</v>
+        <v>মাটির উৎপাদন ক্ষমতা</v>
       </c>
       <c r="F124" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>চন্দ্রমল্লিকা কোন দিবসের ফুল গাছ? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>কোনটি ক্ষারীয় মাটিতে বেশি হয়?</v>
       </c>
       <c r="B125" t="str">
-        <v>খাটো দিবস</v>
+        <v>কমলালেবু</v>
       </c>
       <c r="C125" t="str">
-        <v>দীর্ঘদিবস</v>
+        <v>নারিকেল</v>
       </c>
       <c r="D125" t="str">
-        <v>দিন নিরপেক্ষ</v>
+        <v>আনারস</v>
       </c>
       <c r="E125" t="str">
-        <v>আলোক অসংবেদনশীল</v>
+        <v>কাঁঠাল</v>
       </c>
       <c r="F125" t="str">
         <v>B</v>
@@ -2901,27 +2901,1487 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>নিচের কোন ফসলের সকল জাত ছোট দিনের উদ্ভিদ?</v>
+        <v>নিচের কোনটি উদ্ভিদের গৌণ খনিজ উপাদান?</v>
       </c>
       <c r="B126" t="str">
+        <v>নাইট্রোজেন</v>
+      </c>
+      <c r="C126" t="str">
+        <v>কপার</v>
+      </c>
+      <c r="D126" t="str">
+        <v>পটাসিয়াম</v>
+      </c>
+      <c r="E126" t="str">
+        <v>ফসফরাস</v>
+      </c>
+      <c r="F126" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>সেচের পানির কার্যকারিতা বৃদ্ধি করা যায়-</v>
+      </c>
+      <c r="B127" t="str">
+        <v>দিনে দুইবার সেচ দিয়ে</v>
+      </c>
+      <c r="C127" t="str">
+        <v>আগাছা দমন করে</v>
+      </c>
+      <c r="D127" t="str">
+        <v>সময়মতো সেচ দিয়ে</v>
+      </c>
+      <c r="E127" t="str">
+        <v>সকালবেলা সেচ দিয়ে</v>
+      </c>
+      <c r="F127" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>নিচের কোনটি পানিঘটিত ভূমিক্ষয়ের উদাহরণ? [ঢাকা রেসিডেনশিয়াল মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B128" t="str">
+        <v>সেলটেশন</v>
+      </c>
+      <c r="C128" t="str">
+        <v>লক্ষ ক্ষয়</v>
+      </c>
+      <c r="D128" t="str">
+        <v>গালি ভূমিক্ষয়</v>
+      </c>
+      <c r="E128" t="str">
+        <v>বায়ুপ্রবাহ</v>
+      </c>
+      <c r="F128" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>SRI পদ্ধতির নামান্তর কোনটি? [লায়ন্স স্কুল এন্ড কলেজ, রংপুর]</v>
+      </c>
+      <c r="B129" t="str">
+        <v>AWD</v>
+      </c>
+      <c r="C129" t="str">
+        <v>ADW</v>
+      </c>
+      <c r="D129" t="str">
+        <v>WAD</v>
+      </c>
+      <c r="E129" t="str">
+        <v>RSI</v>
+      </c>
+      <c r="F129" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>নিচের কোনটি বায়ু ভূমিক্ষয়?</v>
+      </c>
+      <c r="B130" t="str">
+        <v>পাত ভূমিক্ষয়</v>
+      </c>
+      <c r="C130" t="str">
+        <v>ধস ভূমিক্ষয়</v>
+      </c>
+      <c r="D130" t="str">
+        <v>গালি ভূমিক্ষয়</v>
+      </c>
+      <c r="E130" t="str">
+        <v>সেলটেশন</v>
+      </c>
+      <c r="F130" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>নিচের কোনটি অধিক অম্লীয় মাটির অম্লমান প্রকাশ করে?</v>
+      </c>
+      <c r="B131" t="str">
+        <v>৪. ৫</v>
+      </c>
+      <c r="C131" t="str">
+        <v>৫. ৮</v>
+      </c>
+      <c r="D131" t="str">
+        <v>৭.০</v>
+      </c>
+      <c r="E131" t="str">
+        <v>৮. ৮</v>
+      </c>
+      <c r="F131" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>প্রাকৃতিক ভূমিক্ষয় হয়- i. বৃষ্টিপাত দ্বারা ii. মানুষের দৈনন্দিন কার্যাবলির দ্বারা iii. প্রবল বায়ুপ্রবাহ দ্বারা নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B132" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C132" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D132" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E132" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F132" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>মাটির আর্দ্রতা সংরক্ষণে কৃত্রিম পদ্ধতিকে কী বলা হয়?</v>
+      </c>
+      <c r="B133" t="str">
+        <v>সেচ</v>
+      </c>
+      <c r="C133" t="str">
+        <v>নিকাশ</v>
+      </c>
+      <c r="D133" t="str">
+        <v>মালচিং</v>
+      </c>
+      <c r="E133" t="str">
+        <v>মৃত্তিকা সংরক্ষণ</v>
+      </c>
+      <c r="F133" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ক্ষারীয় মাটির বৈশিষ্ট্য নিচের কোনটি?</v>
+      </c>
+      <c r="B134" t="str">
+        <v>বিনিময়যোগ্য আয়রনের পবিনিময়যোগ্য আয়রনের পরিমাণ ১৫% এর বেশি।রিমাণ ১৫% এর বেশি।</v>
+      </c>
+      <c r="C134" t="str">
+        <v>লেবু ও ডাল ফসল ভালো হয়</v>
+      </c>
+      <c r="D134" t="str">
+        <v>এ মাটির pH মান ৭ এর নিচে</v>
+      </c>
+      <c r="E134" t="str">
+        <v>মাটিতে ফসফরাসের আধিক্য থাকে</v>
+      </c>
+      <c r="F134" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>বাংলাদেশে ভূমিক্ষয়ের অন্যতম প্রধান কারণ কী? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B135" t="str">
+        <v>নদী ভাঙ্গন</v>
+      </c>
+      <c r="C135" t="str">
+        <v>বৃষ্টিপাত</v>
+      </c>
+      <c r="D135" t="str">
+        <v>বায়ুপ্রবাহ</v>
+      </c>
+      <c r="E135" t="str">
+        <v>বন ধ্বংস</v>
+      </c>
+      <c r="F135" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>নিচের কোনটি অম্ল পছন্দকারী ফসল?</v>
+      </c>
+      <c r="B136" t="str">
+        <v>নারিকেল</v>
+      </c>
+      <c r="C136" t="str">
+        <v>আনারস</v>
+      </c>
+      <c r="D136" t="str">
+        <v>তাল</v>
+      </c>
+      <c r="E136" t="str">
+        <v>খেজুর</v>
+      </c>
+      <c r="F136" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>কোন সেচ পদ্ধতিতে পানির অপচয় অপেক্ষাকৃত বেশি?</v>
+      </c>
+      <c r="B137" t="str">
+        <v>ফারো</v>
+      </c>
+      <c r="C137" t="str">
+        <v>বর্ডার</v>
+      </c>
+      <c r="D137" t="str">
+        <v>ফ্ল্যাড</v>
+      </c>
+      <c r="E137" t="str">
+        <v>ড্রিপ</v>
+      </c>
+      <c r="F137" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>এসআরআই পদ্ধতিতে চারা রোপণের ক্ষেত্রে কোন পদ্ধতি অনুসরণ করা হয়? [খুলনা পাবলিক কলেজ]</v>
+      </c>
+      <c r="B138" t="str">
+        <v>আয়তাকার</v>
+      </c>
+      <c r="C138" t="str">
+        <v>ত্রিকোণাকার</v>
+      </c>
+      <c r="D138" t="str">
+        <v>ষড়ভুজাকার</v>
+      </c>
+      <c r="E138" t="str">
+        <v>বর্গাকার</v>
+      </c>
+      <c r="F138" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>মাটির উৎপাদন ক্ষমতার ভিত্তিতে মাটিকে কয়ভাগে ভাগ করা যায়?</v>
+      </c>
+      <c r="B139" t="str">
+        <v>২ ভাগে</v>
+      </c>
+      <c r="C139" t="str">
+        <v>৩ ভাগে</v>
+      </c>
+      <c r="D139" t="str">
+        <v>৪ ভাগে</v>
+      </c>
+      <c r="E139" t="str">
+        <v>৫ ভাগে</v>
+      </c>
+      <c r="F139" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>কৃষিকাজের জন্য কোন মাটি সবচেয়ে উপযোগী?</v>
+      </c>
+      <c r="B140" t="str">
+        <v>এঁটেল</v>
+      </c>
+      <c r="C140" t="str">
+        <v>বেলে</v>
+      </c>
+      <c r="D140" t="str">
+        <v>দোআঁশ</v>
+      </c>
+      <c r="E140" t="str">
+        <v>পলি</v>
+      </c>
+      <c r="F140" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>রবিউলের জমির মাটি কী ধরনের?</v>
+      </c>
+      <c r="B141" t="str">
+        <v>অম্লীয়</v>
+      </c>
+      <c r="C141" t="str">
+        <v>নিরপেক্ষ</v>
+      </c>
+      <c r="D141" t="str">
+        <v>ক্ষারীয়</v>
+      </c>
+      <c r="E141" t="str">
+        <v>লবণাক্ত</v>
+      </c>
+      <c r="F141" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>বেসিন বা বৃত্তাকার সেচ পদ্ধতিতে সেচ দেওয়া হয়- i. নারিকেল ii. লিচু iii. সূর্যমুখী নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B142" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C142" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D142" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E142" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F142" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>এসআরআই পদ্ধতিতে কোন ফসলে সেচ দেওয়া হয়? [খুলনা পাবলিক কলেজ]</v>
+      </c>
+      <c r="B143" t="str">
+        <v>গম</v>
+      </c>
+      <c r="C143" t="str">
         <v>ধান</v>
       </c>
-      <c r="C126" t="str">
-        <v>গম</v>
-      </c>
-      <c r="D126" t="str">
-        <v>পাট</v>
-      </c>
-      <c r="E126" t="str">
-        <v>চা</v>
-      </c>
-      <c r="F126" t="str">
-        <v>C</v>
+      <c r="D143" t="str">
+        <v>ভুট্টা</v>
+      </c>
+      <c r="E143" t="str">
+        <v>কাউন</v>
+      </c>
+      <c r="F143" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>বেসিক স্লাগ এর রাসায়নিক সংকেত কোনটি?</v>
+      </c>
+      <c r="B144" t="str">
+        <v>$\mathrm{CaSiO}_3$</v>
+      </c>
+      <c r="C144" t="str">
+        <v>$\mathrm{M}_6 \mathrm{O}$</v>
+      </c>
+      <c r="D144" t="str">
+        <v>$\mathrm{Ca}(\mathrm{OH})_2$</v>
+      </c>
+      <c r="E144" t="str">
+        <v>$\mathrm{CaSO}_4 7 \mathrm{H}_3 \mathrm{O}$</v>
+      </c>
+      <c r="F144" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>মাটির আর্দ্রতা সংরক্ষণের কৃত্রিম পদ্ধতিকে কী বলা হয়? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B145" t="str">
+        <v>সেচ</v>
+      </c>
+      <c r="C145" t="str">
+        <v>নিকাশ</v>
+      </c>
+      <c r="D145" t="str">
+        <v>মৃত্তিকা সংরক্ষণ</v>
+      </c>
+      <c r="E145" t="str">
+        <v>মালচিং</v>
+      </c>
+      <c r="F145" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>গাছ মাটি হতে অত্যাবশ্যকীয় কতটি পুষ্টি উপাদান গ্রহণ করে? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B146" t="str">
+        <v>১৭টি</v>
+      </c>
+      <c r="C146" t="str">
+        <v>১৪টি</v>
+      </c>
+      <c r="D146" t="str">
+        <v>১২টি</v>
+      </c>
+      <c r="E146" t="str">
+        <v>১০টি</v>
+      </c>
+      <c r="F146" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>উর্বরতার ভিত্তিতে মাটিকে কতভাগে ভাগ করা যায়?</v>
+      </c>
+      <c r="B147" t="str">
+        <v>২ ভাগে</v>
+      </c>
+      <c r="C147" t="str">
+        <v>৩ ভাগে</v>
+      </c>
+      <c r="D147" t="str">
+        <v>৪ ভাগে</v>
+      </c>
+      <c r="E147" t="str">
+        <v>৫ ভাগে</v>
+      </c>
+      <c r="F147" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>কোন ধরনের সেচ পাহাড়ি এলাকার জন্য উপযোগী।</v>
+      </c>
+      <c r="B148" t="str">
+        <v>ভূনিম্নস্থ সেচ</v>
+      </c>
+      <c r="C148" t="str">
+        <v>কন্টুর নালা পদ্ধতি</v>
+      </c>
+      <c r="D148" t="str">
+        <v>ফোয়ারা পদ্ধতি</v>
+      </c>
+      <c r="E148" t="str">
+        <v>ড্রিপ / ট্রিকল পদ্ধতি</v>
+      </c>
+      <c r="F148" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>লাল লিটমাস ক্ষারীয় মৃত্তিকা দ্রবণকে কী করে?</v>
+      </c>
+      <c r="B149" t="str">
+        <v>সবুজ</v>
+      </c>
+      <c r="C149" t="str">
+        <v>বাদামি</v>
+      </c>
+      <c r="D149" t="str">
+        <v>হলুদ</v>
+      </c>
+      <c r="E149" t="str">
+        <v>নীল</v>
+      </c>
+      <c r="F149" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>ক্ষারীয় মাটির pH মান কত?</v>
+      </c>
+      <c r="B150" t="str">
+        <v>৫.৯</v>
+      </c>
+      <c r="C150" t="str">
+        <v>৬.০</v>
+      </c>
+      <c r="D150" t="str">
+        <v>৭.০</v>
+      </c>
+      <c r="E150" t="str">
+        <v>&gt; ৭.০</v>
+      </c>
+      <c r="F150" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>মাটির অম্লত্ত্বের জন্য দায়ী কোনটি?</v>
+      </c>
+      <c r="B151" t="str">
+        <v>অধিক চুন ব্যবহার</v>
+      </c>
+      <c r="C151" t="str">
+        <v>সোডিয়াম যুক্ত সেচের পানি</v>
+      </c>
+      <c r="D151" t="str">
+        <v>অধিক বৃষ্টিপাত ও চুয়ালি</v>
+      </c>
+      <c r="E151" t="str">
+        <v>জৈব সার বেশি ব্যবহার</v>
+      </c>
+      <c r="F151" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>গাছ মাটি হতে অত্যাবশ্যকীয় কতটি পুষ্টি উপাদান গ্রহণ করে?</v>
+      </c>
+      <c r="B152" t="str">
+        <v>১৭টি</v>
+      </c>
+      <c r="C152" t="str">
+        <v>১৪টি</v>
+      </c>
+      <c r="D152" t="str">
+        <v>১২টি</v>
+      </c>
+      <c r="E152" t="str">
+        <v>১০টি</v>
+      </c>
+      <c r="F152" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>ধান চাষে যে পদ্ধতিতে সেচ প্রদান করা হয়ে থাকে- i. মুক্ত প্লাবন ii. বর্ডার iii. চেক বেসিন নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B153" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C153" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D153" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E153" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F153" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>উদ্দীপকে উল্লিখিত উপাদান ব্যবহার করে ছক্কূ মিয়ার জমির-</v>
+      </c>
+      <c r="B154" t="str">
+        <v>ভৌত গঠন উন্নত হয়</v>
+      </c>
+      <c r="C154" t="str">
+        <v>মাটির উর্বরতা বৃদ্ধি পায়</v>
+      </c>
+      <c r="D154" t="str">
+        <v>রোগের আক্রমণ হ্রাস পায়</v>
+      </c>
+      <c r="E154" t="str">
+        <v>পোকা-মাকড়ের আক্রমণ হ্রাস পায়</v>
+      </c>
+      <c r="F154" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>প্রতি ফসল মৌসুমে কর্তিত ফসলের মাধ্যমে অপসারিত হয়- [রাজেন্দ্রপুর ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, গাজীপুর] i. নাইট্রোজেন ii. টিএসপি iii. জৈব পদার্থ নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B155" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C155" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D155" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E155" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F155" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>SRI পদ্ধতিতে ব্যবহৃত ধানের চারার বয়স কত? [পটিয়া সরকারি কলেজ, চট্টগ্রাম]</v>
+      </c>
+      <c r="B156" t="str">
+        <v>১০-১৫ দিন</v>
+      </c>
+      <c r="C156" t="str">
+        <v>২০-২৫ দিন</v>
+      </c>
+      <c r="D156" t="str">
+        <v>২৫-৩০ দিন</v>
+      </c>
+      <c r="E156" t="str">
+        <v>৩০-৩৫ দিন</v>
+      </c>
+      <c r="F156" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>AWD পদ্ধতির মূল লক্ষ্য কী?</v>
+      </c>
+      <c r="B157" t="str">
+        <v>পানি ও জ্বালানি সাশ্রয় করা</v>
+      </c>
+      <c r="C157" t="str">
+        <v>পোকা-মাকড়ের উপদ্রব কমানো</v>
+      </c>
+      <c r="D157" t="str">
+        <v>ফলন বেশি হয়</v>
+      </c>
+      <c r="E157" t="str">
+        <v>ফসল আগাম পাকে</v>
+      </c>
+      <c r="F157" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>ভূমিক্ষয় রোধ করা যায় কীভাবে?</v>
+      </c>
+      <c r="B158" t="str">
+        <v>আগাছা দমনের মাধ্যমে</v>
+      </c>
+      <c r="C158" t="str">
+        <v>রাসায়নিক সার ব্যবহার করে</v>
+      </c>
+      <c r="D158" t="str">
+        <v>ফসল ব্যবস্থপনা অবলম্বন করে</v>
+      </c>
+      <c r="E158" t="str">
+        <v>পাহাড়ের ঢাল কেটে</v>
+      </c>
+      <c r="F158" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>পাহাড়ি ভূমিক্ষয় রোধের প্রধান উপায় কোনটি?</v>
+      </c>
+      <c r="B159" t="str">
+        <v>ধাপে চাষ করা</v>
+      </c>
+      <c r="C159" t="str">
+        <v>জাবড়া প্রয়োগ করা</v>
+      </c>
+      <c r="D159" t="str">
+        <v>জমি কম চাষ করা</v>
+      </c>
+      <c r="E159" t="str">
+        <v>জমিকে বিশ্রাম দেওয়া</v>
+      </c>
+      <c r="F159" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>AWD পদ্ধতির মূল লক্ষ্য কী?</v>
+      </c>
+      <c r="B160" t="str">
+        <v>পানি ও জ্বালানি সাশ্রয় করা</v>
+      </c>
+      <c r="C160" t="str">
+        <v>পোকা-মাকড়ের উপদ্রব কমানো</v>
+      </c>
+      <c r="D160" t="str">
+        <v>ফলন বেশি হয়</v>
+      </c>
+      <c r="E160" t="str">
+        <v>ফসল আগাম পাকে</v>
+      </c>
+      <c r="F160" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>নিচের কোন ফসল ক্ষার মাটিতে ভালো জন্মে?</v>
+      </c>
+      <c r="B161" t="str">
+        <v>আনারস</v>
+      </c>
+      <c r="C161" t="str">
+        <v>নারিকেল</v>
+      </c>
+      <c r="D161" t="str">
+        <v>তাল</v>
+      </c>
+      <c r="E161" t="str">
+        <v>খেজুর</v>
+      </c>
+      <c r="F161" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>কোনটি প্রাকৃতিক ভূমিক্ষয়ের কারণ?</v>
+      </c>
+      <c r="B162" t="str">
+        <v>ভূমিকৰ্ষণ</v>
+      </c>
+      <c r="C162" t="str">
+        <v>নদী ভাঙ্গন</v>
+      </c>
+      <c r="D162" t="str">
+        <v>পানি সেচ</v>
+      </c>
+      <c r="E162" t="str">
+        <v>পাহাড় কাটা</v>
+      </c>
+      <c r="F162" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>SRI (ধান চাষের নিবিড় পদ্ধতি) পদ্ধতিতে ধান চাষ করলে- [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর] i. ফলন বেশি হয় ii. ফসলের জীবনকাল বেশি হয় iii. কম মিথেন গ্যাস তৈরি হয় নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B163" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C163" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D163" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E163" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F163" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>SRI পদ্ধতিতে কোন সেচ পদ্ধতি ব্যবহার করা হয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B164" t="str">
+        <v>প্লাবন</v>
+      </c>
+      <c r="C164" t="str">
+        <v>এ ডব্লিউ ডি</v>
+      </c>
+      <c r="D164" t="str">
+        <v>ফোয়ারা</v>
+      </c>
+      <c r="E164" t="str">
+        <v>নালা</v>
+      </c>
+      <c r="F164" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>বায়ু প্রবাহ দ্বারা বাংলাদেশের কোন অঞ্চলে ভূমিক্ষয় হয়?</v>
+      </c>
+      <c r="B165" t="str">
+        <v>রাজশাহী ও দিনাজপুর</v>
+      </c>
+      <c r="C165" t="str">
+        <v>ময়মনসিংহ ও জামালপুর</v>
+      </c>
+      <c r="D165" t="str">
+        <v>বরিশাল ও পটুয়াখালী</v>
+      </c>
+      <c r="E165" t="str">
+        <v>মাদারীপুর ও ফরিদপুর</v>
+      </c>
+      <c r="F165" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>জমির লবণাক্ততা দূরীকরণে কোনটি ব্যবহার করা যায়? [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, টঙ্গী, গাজীপুর]</v>
+      </c>
+      <c r="B166" t="str">
+        <v>সালফার</v>
+      </c>
+      <c r="C166" t="str">
+        <v>জিপসাম</v>
+      </c>
+      <c r="D166" t="str">
+        <v>ক্যালসাইট</v>
+      </c>
+      <c r="E166" t="str">
+        <v>ট্রাইকোর্ডামা</v>
+      </c>
+      <c r="F166" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>কৃষি জমিতে চুন ব্যবহার করা হয় কেন?</v>
+      </c>
+      <c r="B167" t="str">
+        <v>ক্ষারত্ব সংশোধনে</v>
+      </c>
+      <c r="C167" t="str">
+        <v>অম্লত্ব সংশোধনে</v>
+      </c>
+      <c r="D167" t="str">
+        <v>লবণাক্ততা দূরীকরণে</v>
+      </c>
+      <c r="E167" t="str">
+        <v>পানি ধারণ ক্ষমতা বাড়াতে</v>
+      </c>
+      <c r="F167" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>নিচের কোনটি অল্প প্রধান শিলা।</v>
+      </c>
+      <c r="B168" t="str">
+        <v>ফেলসপার</v>
+      </c>
+      <c r="C168" t="str">
+        <v>গ্রানাইট</v>
+      </c>
+      <c r="D168" t="str">
+        <v>ডলোমাইট</v>
+      </c>
+      <c r="E168" t="str">
+        <v>সিলিকা</v>
+      </c>
+      <c r="F168" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>SRI পদ্ধতিতে বীজের অঙ্কুরোদগমের হার শতকরা কত হতে হয়? [আল-আমিন একাডেমী স্কুল এন্ড কলেজ, চাঁদপুর]</v>
+      </c>
+      <c r="B169" t="str">
+        <v>৮৫-৭৫</v>
+      </c>
+      <c r="C169" t="str">
+        <v>৭৫-৮০</v>
+      </c>
+      <c r="D169" t="str">
+        <v>৭০-৭৫</v>
+      </c>
+      <c r="E169" t="str">
+        <v>৮০-৮৫</v>
+      </c>
+      <c r="F169" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>ফল গাছে কোন পদ্ধতিতে সেচ দেওয়া হয়?</v>
+      </c>
+      <c r="B170" t="str">
+        <v>নালা</v>
+      </c>
+      <c r="C170" t="str">
+        <v>ছিটানো</v>
+      </c>
+      <c r="D170" t="str">
+        <v>বেসিন</v>
+      </c>
+      <c r="E170" t="str">
+        <v>প্লাবন</v>
+      </c>
+      <c r="F170" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>নিচের কোনটি উদ্ভিদের মুখ্য খনিজ উপাদান?</v>
+      </c>
+      <c r="B171" t="str">
+        <v>ফসফরাস</v>
+      </c>
+      <c r="C171" t="str">
+        <v>জিংক</v>
+      </c>
+      <c r="D171" t="str">
+        <v>ক্লোরিন</v>
+      </c>
+      <c r="E171" t="str">
+        <v>বোরন</v>
+      </c>
+      <c r="F171" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>সবচেয়ে সাশ্রয়ী পানি সেচ পদ্ধতি কোনটি?</v>
+      </c>
+      <c r="B172" t="str">
+        <v>রিং-বেসিন</v>
+      </c>
+      <c r="C172" t="str">
+        <v>নালা</v>
+      </c>
+      <c r="D172" t="str">
+        <v>ড্রিপ</v>
+      </c>
+      <c r="E172" t="str">
+        <v>চেক বেসিন</v>
+      </c>
+      <c r="F172" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>ধান গাছে সেচ দেওয়ার পদ্ধতি কোনটি? [সোনার বাংলা কলেজ, কুমিল্লা]</v>
+      </c>
+      <c r="B173" t="str">
+        <v>ATP</v>
+      </c>
+      <c r="C173" t="str">
+        <v>ATW</v>
+      </c>
+      <c r="D173" t="str">
+        <v>AWD</v>
+      </c>
+      <c r="E173" t="str">
+        <v>AUD</v>
+      </c>
+      <c r="F173" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>SRI পদ্ধতিতে ধান চাষ করলে ধানের ফলন শতকরা কত ভাগ বৃদ্ধি পায়? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ]</v>
+      </c>
+      <c r="B174" t="str">
+        <v>১০</v>
+      </c>
+      <c r="C174" t="str">
+        <v>১৫</v>
+      </c>
+      <c r="D174" t="str">
+        <v>২০</v>
+      </c>
+      <c r="E174" t="str">
+        <v>২৫</v>
+      </c>
+      <c r="F174" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>জমিতে জৈব পদার্থের পরিমাণ শতকরা কত ভাগ থাকা উচিত? [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর]</v>
+      </c>
+      <c r="B175" t="str">
+        <v>১ ভাগ</v>
+      </c>
+      <c r="C175" t="str">
+        <v>৫ ভাগ</v>
+      </c>
+      <c r="D175" t="str">
+        <v>১০ ভাগ</v>
+      </c>
+      <c r="E175" t="str">
+        <v>২৫ ভাগ</v>
+      </c>
+      <c r="F175" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>ফারো সেচ পদ্ধতিতে- i. পানির অপচয় কম হয় ii. ভূমিক্ষয়ের সম্বাবনা কম iii. শ্রমিক কম লাগে নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B176" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C176" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D176" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E176" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F176" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>এসআরআই পদ্ধতিতে প্রতি গুছিতে কয়টি চারা রোপণ করা যায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B177" t="str">
+        <v>১টি</v>
+      </c>
+      <c r="C177" t="str">
+        <v>২টি</v>
+      </c>
+      <c r="D177" t="str">
+        <v>৩টি</v>
+      </c>
+      <c r="E177" t="str">
+        <v>৪টি</v>
+      </c>
+      <c r="F177" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>কোন মাটির পানি ধারণ ক্ষমতা সবচেয়ে কম?</v>
+      </c>
+      <c r="B178" t="str">
+        <v>এঁটেল</v>
+      </c>
+      <c r="C178" t="str">
+        <v>পলি</v>
+      </c>
+      <c r="D178" t="str">
+        <v>দোআঁশ</v>
+      </c>
+      <c r="E178" t="str">
+        <v>বেলে</v>
+      </c>
+      <c r="F178" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>ধৈঞ্চা গাছে কোন পুষ্টি উপাদানটি বেশি পরিমাণে থাকে?</v>
+      </c>
+      <c r="B179" t="str">
+        <v>নাইট্রোজেন</v>
+      </c>
+      <c r="C179" t="str">
+        <v>ফসফরাস</v>
+      </c>
+      <c r="D179" t="str">
+        <v>পটাশিয়াম</v>
+      </c>
+      <c r="E179" t="str">
+        <v>সালফার</v>
+      </c>
+      <c r="F179" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>নিচের কোনটি অণুজীব সার?</v>
+      </c>
+      <c r="B180" t="str">
+        <v>রাইজোবিয়াম সার</v>
+      </c>
+      <c r="C180" t="str">
+        <v>কম্পোস্ট সার</v>
+      </c>
+      <c r="D180" t="str">
+        <v>সবুজ সার</v>
+      </c>
+      <c r="E180" t="str">
+        <v>খামারজাত সার</v>
+      </c>
+      <c r="F180" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>গমের ক্ষেতে প্রথম সেচটি কখন দেওয়া প্রয়োজন হয়? [খুলনা পাবলিক কলেজ]</v>
+      </c>
+      <c r="B181" t="str">
+        <v>কুশি গজানোর সময়</v>
+      </c>
+      <c r="C181" t="str">
+        <v>শীষ গজানোর সময়</v>
+      </c>
+      <c r="D181" t="str">
+        <v>মুকুট মূল গজানোর সময়</v>
+      </c>
+      <c r="E181" t="str">
+        <v>পুষ্পায়নের সময়</v>
+      </c>
+      <c r="F181" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>চুন দ্রব্য হলো- i. কেলাসাইট ii. জিপসাম iii. বেসিক স্ল্যাগ নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C182" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D182" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E182" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F182" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>কৃষি জমিতে চুন ব্যবহার করা হয় কেন?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>ক্ষারত্ব সংশোধনে</v>
+      </c>
+      <c r="C183" t="str">
+        <v>অম্লত্ব সংশোধনে</v>
+      </c>
+      <c r="D183" t="str">
+        <v>লবণাক্ততা দূরীকরণে</v>
+      </c>
+      <c r="E183" t="str">
+        <v>পানি ধারণ ক্ষমতা বাড়াতে</v>
+      </c>
+      <c r="F183" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>SRI পদ্ধতিতে কতদিন বয়সের ধানের চারা রোপণ করতে হয়? [ঢাকা রেসিডেনসিয়াল মডেল কলেজ; ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, মোমেনশাহী]</v>
+      </c>
+      <c r="B184" t="str">
+        <v>১০-১৫ দিন</v>
+      </c>
+      <c r="C184" t="str">
+        <v>১৫-২০ দিন</v>
+      </c>
+      <c r="D184" t="str">
+        <v>২০-২৫ দিন</v>
+      </c>
+      <c r="E184" t="str">
+        <v>২৫-৩০ দিন</v>
+      </c>
+      <c r="F184" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>বালুময় পাহাড়ি জমিতে সেচের জন্য কোন পদ্ধতি উপযোগী?</v>
+      </c>
+      <c r="B185" t="str">
+        <v>ফোয়ারা সেচ</v>
+      </c>
+      <c r="C185" t="str">
+        <v>প্লাবন সেচ</v>
+      </c>
+      <c r="D185" t="str">
+        <v>আইল সেচ</v>
+      </c>
+      <c r="E185" t="str">
+        <v>নালা সেচ</v>
+      </c>
+      <c r="F185" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>SRI পদ্ধতির বৈশিষ্ট্য- [ঘাটাইল ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, টাংগাইল] i. একটি গোছায় একটি চারা ii. বর্গাকার পদ্ধতিতে রোপন iii. পালাক্রমে ভিজানো ও শুকানো নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B186" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C186" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D186" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E186" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F186" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ইনোকুলাম কি জাতীয় সার?</v>
+      </c>
+      <c r="B187" t="str">
+        <v>জৈব</v>
+      </c>
+      <c r="C187" t="str">
+        <v>রাসায়নিক</v>
+      </c>
+      <c r="D187" t="str">
+        <v>অণুজীব</v>
+      </c>
+      <c r="E187" t="str">
+        <v>কম্পোস্ট</v>
+      </c>
+      <c r="F187" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>নিচের চিত্রটি লক্ষ কর এবং প্রশ্নের উত্তর দাও: [আব্দুল কাদির মোল্লা সিটি কলেজ, নরসিংদী] Q. চিত্রে প্রদর্শিত পদ্ধতিতে প্রতি গোছায় কয়টি চারা রোপণ করতে হয়</v>
+      </c>
+      <c r="B188" t="str">
+        <v>১</v>
+      </c>
+      <c r="C188" t="str">
+        <v>২</v>
+      </c>
+      <c r="D188" t="str">
+        <v>৩</v>
+      </c>
+      <c r="E188" t="str">
+        <v>৪</v>
+      </c>
+      <c r="F188" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>SRI পদ্ধতির নামান্তর কোনটি?</v>
+      </c>
+      <c r="B189" t="str">
+        <v>AWD</v>
+      </c>
+      <c r="C189" t="str">
+        <v>ADW</v>
+      </c>
+      <c r="D189" t="str">
+        <v>WAD</v>
+      </c>
+      <c r="E189" t="str">
+        <v>RSI</v>
+      </c>
+      <c r="F189" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>নিচের চিত্রটি লক্ষ কর এবং প্রশ্নের উত্তর দাও: [আব্দুল কাদির মোল্লা সিটি কলেজ, নরসিংদী] Q. উল্লিখিত পদ্ধতিতে চাষাবাদের ফলে- i. ফলন বৃদ্ধি পায় ii. কুশির সংখ্যা বৃদ্ধি পায় iii. ফসলের মেয়াদ কমে যায় নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B190" t="str">
+        <v>iii</v>
+      </c>
+      <c r="C190" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="D190" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="E190" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F190" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>মাটি সংশোধন করলে কী ঘটে?</v>
+      </c>
+      <c r="B191" t="str">
+        <v>মাটির আর্দ্রতা বৃদ্ধি</v>
+      </c>
+      <c r="C191" t="str">
+        <v>ক্ষারত্ব বাড়ে</v>
+      </c>
+      <c r="D191" t="str">
+        <v>অম্লত্ব বাড়ে</v>
+      </c>
+      <c r="E191" t="str">
+        <v>মাটির উর্বরতা বৃদ্ধি পায়</v>
+      </c>
+      <c r="F191" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>সেচের সূচনা হয় কোথায়?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>মিসরে</v>
+      </c>
+      <c r="C192" t="str">
+        <v>জাপানে</v>
+      </c>
+      <c r="D192" t="str">
+        <v>রাশিয়ায়</v>
+      </c>
+      <c r="E192" t="str">
+        <v>যুক্তরাজ্যে</v>
+      </c>
+      <c r="F192" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>কৃষিকাজের জন্য কোন মাটি সবচেয়ে উপযোগী?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>এঁটেল</v>
+      </c>
+      <c r="C193" t="str">
+        <v>বেলে</v>
+      </c>
+      <c r="D193" t="str">
+        <v>দোআঁশ</v>
+      </c>
+      <c r="E193" t="str">
+        <v>পলি</v>
+      </c>
+      <c r="F193" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>ক্ষারজ শিলা হলো- i, গ্রানাইট i i. ডলোমাইট i ii. ক্যালসাইট নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B194" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="C194" t="str">
+        <v>ii ও iii</v>
+      </c>
+      <c r="D194" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E194" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F194" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>কোন উপাদানটিকে 'মাটির প্রাণ' বলা হয়? [আব্দুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
+      </c>
+      <c r="B195" t="str">
+        <v>বায়ু</v>
+      </c>
+      <c r="C195" t="str">
+        <v>পানি</v>
+      </c>
+      <c r="D195" t="str">
+        <v>জৈব পদার্থ</v>
+      </c>
+      <c r="E195" t="str">
+        <v>খনিজ পদার্থ</v>
+      </c>
+      <c r="F195" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>পাহাড়ি জমিতে কোন ধরনের ভূমিক্ষয় হয়?</v>
+      </c>
+      <c r="B196" t="str">
+        <v>রিল</v>
+      </c>
+      <c r="C196" t="str">
+        <v>গালি</v>
+      </c>
+      <c r="D196" t="str">
+        <v>ধস</v>
+      </c>
+      <c r="E196" t="str">
+        <v>আস্তরণ</v>
+      </c>
+      <c r="F196" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>মাটিতে অম্লত্ব মাত্রা বৃদ্ধি হলে যে পুষ্টি উপাদান বেশি মাত্রায় দ্রবণীয় হয়- i. নাইট্রোজেন ii. পটাসিয়াম iii. সালফার নিচের কোনটি সঠিক?</v>
+      </c>
+      <c r="B197" t="str">
+        <v>i</v>
+      </c>
+      <c r="C197" t="str">
+        <v>i ও ii</v>
+      </c>
+      <c r="D197" t="str">
+        <v>i ও iii</v>
+      </c>
+      <c r="E197" t="str">
+        <v>i, ii ও iii</v>
+      </c>
+      <c r="F197" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>প্রশম বা নিরপেক্ষ মাটির অম্লমান (pH) কোনটি?</v>
+      </c>
+      <c r="B198" t="str">
+        <v>৭ এর কম</v>
+      </c>
+      <c r="C198" t="str">
+        <v>৭</v>
+      </c>
+      <c r="D198" t="str">
+        <v>৭ এর বেশি</v>
+      </c>
+      <c r="E198" t="str">
+        <v>৮ এর বেশি</v>
+      </c>
+      <c r="F198" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>বাংলাদেশে ভূমিক্ষয়ের অন্যতম প্রধান কারণ কী?</v>
+      </c>
+      <c r="B199" t="str">
+        <v>নদী ভাঙ্গন</v>
+      </c>
+      <c r="C199" t="str">
+        <v>বৃষ্টিপাত</v>
+      </c>
+      <c r="D199" t="str">
+        <v>বায়ুপ্রবাহ</v>
+      </c>
+      <c r="E199" t="str">
+        <v>বন ধ্বংস</v>
+      </c>
+      <c r="F199" t="str">
+        <v>B</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F126"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F199"/>
   </ignoredErrors>
 </worksheet>
 </file>